--- a/public/exports/62761113.xlsx
+++ b/public/exports/62761113.xlsx
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098038</t>
+          <t xml:space="preserve">209314</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F9">
-        <v>3669</v>
+        <v>406</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098046</t>
+          <t xml:space="preserve">209704</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F10">
-        <v>12973</v>
+        <v>1143</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -536,11 +536,11 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F11">
-        <v>6908</v>
+        <v>12973</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -586,11 +586,11 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F12">
-        <v>2492</v>
+        <v>6908</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -636,11 +636,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F13">
-        <v>632</v>
+        <v>2492</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098143</t>
+          <t xml:space="preserve">2098046</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F14">
-        <v>1146</v>
+        <v>632</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2099385</t>
+          <t xml:space="preserve">2099386</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F15">
-        <v>1460</v>
+        <v>348</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2099385</t>
+          <t xml:space="preserve">212352, 212353, 212354, 212355, 212357, 212358, 212356, 212359</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F16">
-        <v>1460</v>
+        <v>360</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2099386</t>
+          <t xml:space="preserve">214564</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F17">
-        <v>348</v>
+        <v>1369</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">500360, 500361, 500362, 500364, 7151452</t>
+          <t xml:space="preserve">214564, 214565</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F18">
-        <v>5035</v>
+        <v>5862</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">711911, 2099464</t>
+          <t xml:space="preserve">214566</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F19">
-        <v>325</v>
+        <v>2076</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">711916, 2085366</t>
+          <t xml:space="preserve">214588</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F20">
-        <v>2041</v>
+        <v>8344</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">220694, 220695</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F21">
-        <v>448</v>
+        <v>1924</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">222533, 222534</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F22">
-        <v>448</v>
+        <v>316</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">222534</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F23">
-        <v>266</v>
+        <v>316</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">500360, 500361, 500362, 500364, 7151452</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F24">
-        <v>380</v>
+        <v>5035</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">711911, 2099464</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F25">
-        <v>672</v>
+        <v>325</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1286,11 +1286,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F26">
-        <v>380</v>
+        <v>448</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1336,11 +1336,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F27">
-        <v>380</v>
+        <v>266</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1386,11 +1386,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F28">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1436,11 +1436,11 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F29">
-        <v>306</v>
+        <v>380</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1486,11 +1486,11 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F30">
-        <v>450</v>
+        <v>380</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1536,11 +1536,11 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F31">
-        <v>306</v>
+        <v>400</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F32">
@@ -1636,11 +1636,11 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F33">
-        <v>672</v>
+        <v>450</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1686,11 +1686,11 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F34">
-        <v>672</v>
+        <v>306</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1736,11 +1736,11 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F35">
-        <v>448</v>
+        <v>306</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1786,11 +1786,11 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F36">
-        <v>448</v>
+        <v>672</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F37">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F38">
@@ -1936,11 +1936,11 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F39">
-        <v>672</v>
+        <v>448</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,16 +1981,16 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">711942, 9522597</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F40">
-        <v>312</v>
+        <v>672</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,16 +2031,16 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">711977, 2085091</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F41">
-        <v>4665</v>
+        <v>448</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2081,16 +2081,16 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">711981, 2099445</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F42">
-        <v>1020</v>
+        <v>672</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2131,16 +2131,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">711982, 2099475</t>
+          <t xml:space="preserve">711942, 9522597</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F43">
-        <v>551</v>
+        <v>312</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">711983, 2088539</t>
+          <t xml:space="preserve">711981, 2099445</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="F44">
-        <v>1272</v>
+        <v>1020</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2431,16 +2431,16 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8705979</t>
+          <t xml:space="preserve">8777390</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F49">
-        <v>254</v>
+        <v>691</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2481,30 +2481,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777390</t>
+          <t xml:space="preserve">2017118</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F50">
-        <v>691</v>
+        <v>1200</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200021869</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-10-06</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2531,30 +2531,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9937922</t>
+          <t xml:space="preserve">2085364</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F51">
-        <v>336</v>
+        <v>2047</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200024430</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-11-24</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2581,25 +2581,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017118</t>
+          <t xml:space="preserve">8705979</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F52">
-        <v>1200</v>
+        <v>254</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021869</t>
+          <t xml:space="preserve">200024688</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-06</t>
+          <t xml:space="preserve">2019-11-27</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085364</t>
+          <t xml:space="preserve">8777687</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2640,16 +2640,16 @@
         </is>
       </c>
       <c r="F53">
-        <v>2047</v>
+        <v>10924</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024430</t>
+          <t xml:space="preserve">200043874</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-24</t>
+          <t xml:space="preserve">2021-01-04</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2681,25 +2681,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777687</t>
+          <t xml:space="preserve">2098038</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F54">
-        <v>10924</v>
+        <v>3669</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043875</t>
+          <t xml:space="preserve">200054667</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-04</t>
+          <t xml:space="preserve">2021-11-09</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,25 +2731,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123186</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F55">
-        <v>4930</v>
+        <v>448</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">200048635</t>
+          <t xml:space="preserve">200056555</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-29</t>
+          <t xml:space="preserve">2022-01-10</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2781,25 +2781,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F56">
-        <v>1866</v>
+        <v>672</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057567</t>
+          <t xml:space="preserve">200056559</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-21</t>
+          <t xml:space="preserve">2022-01-10</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">212352, 212353, 212354, 212355, 212357, 212358, 212356, 212359</t>
+          <t xml:space="preserve">2012604</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3140,26 +3140,26 @@
         </is>
       </c>
       <c r="F63">
-        <v>360</v>
+        <v>7984</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311084106</t>
+          <t xml:space="preserve">311230939</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-19</t>
+          <t xml:space="preserve">2027-02-27</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012604</t>
+          <t xml:space="preserve">2089300</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3190,16 +3190,16 @@
         </is>
       </c>
       <c r="F64">
-        <v>7984</v>
+        <v>1625</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230939</t>
+          <t xml:space="preserve">311242205</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-27</t>
+          <t xml:space="preserve">2027-04-21</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3231,25 +3231,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2089300</t>
+          <t xml:space="preserve">711982, 2099475</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F65">
-        <v>1625</v>
+        <v>551</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242205</t>
+          <t xml:space="preserve">311356775</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-21</t>
+          <t xml:space="preserve">2029-01-28</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3781,25 +3781,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123186</t>
+          <t xml:space="preserve">2013620</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F76">
-        <v>6329</v>
+        <v>1400</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311415818</t>
+          <t xml:space="preserve">311417096</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-06</t>
+          <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,25 +3831,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123186</t>
+          <t xml:space="preserve">2014070</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F77">
-        <v>764</v>
+        <v>782</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311415823</t>
+          <t xml:space="preserve">311417092</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-06</t>
+          <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,20 +3881,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013620</t>
+          <t xml:space="preserve">2014490</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F78">
-        <v>1400</v>
+        <v>2207</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417096</t>
+          <t xml:space="preserve">311417115</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014070</t>
+          <t xml:space="preserve">2017046</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3940,11 +3940,11 @@
         </is>
       </c>
       <c r="F79">
-        <v>782</v>
+        <v>329</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417092</t>
+          <t xml:space="preserve">311417095</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3981,20 +3981,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014490</t>
+          <t xml:space="preserve">2018039</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F80">
-        <v>2207</v>
+        <v>460</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417115</t>
+          <t xml:space="preserve">311417148</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017046</t>
+          <t xml:space="preserve">2084680</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4040,11 +4040,11 @@
         </is>
       </c>
       <c r="F81">
-        <v>329</v>
+        <v>760</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417095</t>
+          <t xml:space="preserve">311417120</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4081,20 +4081,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018039</t>
+          <t xml:space="preserve">2085363</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F82">
-        <v>460</v>
+        <v>1927</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417148</t>
+          <t xml:space="preserve">311417112</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2084680</t>
+          <t xml:space="preserve">7295209</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4140,11 +4140,11 @@
         </is>
       </c>
       <c r="F83">
-        <v>760</v>
+        <v>720</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417120</t>
+          <t xml:space="preserve">311417091</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085363</t>
+          <t xml:space="preserve">9883414</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4190,11 +4190,11 @@
         </is>
       </c>
       <c r="F84">
-        <v>1927</v>
+        <v>4672</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417112</t>
+          <t xml:space="preserve">311417114</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4231,25 +4231,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">220694, 220695</t>
+          <t xml:space="preserve">2012391</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F85">
-        <v>1924</v>
+        <v>471</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417101</t>
+          <t xml:space="preserve">311418137</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-14</t>
+          <t xml:space="preserve">2030-01-21</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">222533, 222534</t>
+          <t xml:space="preserve">2012253</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F86">
-        <v>316</v>
+        <v>484</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417100</t>
+          <t xml:space="preserve">311418880</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-14</t>
+          <t xml:space="preserve">2030-01-24</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">222534</t>
+          <t xml:space="preserve">2010230</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4340,16 +4340,16 @@
         </is>
       </c>
       <c r="F87">
-        <v>316</v>
+        <v>639</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417100</t>
+          <t xml:space="preserve">311423941</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-14</t>
+          <t xml:space="preserve">2030-02-21</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">7295209</t>
+          <t xml:space="preserve">2018588</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4390,16 +4390,16 @@
         </is>
       </c>
       <c r="F88">
-        <v>720</v>
+        <v>895</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417091</t>
+          <t xml:space="preserve">311423940</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-14</t>
+          <t xml:space="preserve">2030-02-21</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9883414</t>
+          <t xml:space="preserve">2010032</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4440,16 +4440,16 @@
         </is>
       </c>
       <c r="F89">
-        <v>4672</v>
+        <v>731</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417114</t>
+          <t xml:space="preserve">311424128</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-14</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4481,25 +4481,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012391</t>
+          <t xml:space="preserve">2011266</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F90">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418137</t>
+          <t xml:space="preserve">311424125</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-21</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012253</t>
+          <t xml:space="preserve">2013432</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4540,16 +4540,16 @@
         </is>
       </c>
       <c r="F91">
-        <v>484</v>
+        <v>507</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418880</t>
+          <t xml:space="preserve">311424132</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-24</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4581,25 +4581,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">9123186</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F92">
-        <v>1680</v>
+        <v>6329</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418879</t>
+          <t xml:space="preserve">311425249</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-24</t>
+          <t xml:space="preserve">2030-02-28</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4631,25 +4631,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010230</t>
+          <t xml:space="preserve">9123186</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F93">
-        <v>639</v>
+        <v>2404</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311423941</t>
+          <t xml:space="preserve">311425249</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-21</t>
+          <t xml:space="preserve">2030-02-28</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4681,25 +4681,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018588</t>
+          <t xml:space="preserve">9123186</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F94">
-        <v>895</v>
+        <v>614</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311423940</t>
+          <t xml:space="preserve">311425249</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-21</t>
+          <t xml:space="preserve">2030-02-28</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4731,25 +4731,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010032</t>
+          <t xml:space="preserve">9123186</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F95">
-        <v>731</v>
+        <v>4930</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424128</t>
+          <t xml:space="preserve">311425249</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2030-02-28</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4781,25 +4781,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011266</t>
+          <t xml:space="preserve">9123186</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F96">
-        <v>482</v>
+        <v>764</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424125</t>
+          <t xml:space="preserve">311425249</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2030-02-28</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013432</t>
+          <t xml:space="preserve">2009443</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424132</t>
+          <t xml:space="preserve">311427845</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2030-03-13</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,25 +4881,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123186</t>
+          <t xml:space="preserve">2013032</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F98">
-        <v>2404</v>
+        <v>634</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311425252</t>
+          <t xml:space="preserve">311427844</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-28</t>
+          <t xml:space="preserve">2030-03-13</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,25 +4931,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123186</t>
+          <t xml:space="preserve">2016721</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F99">
-        <v>614</v>
+        <v>754</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311425251</t>
+          <t xml:space="preserve">311427843</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-28</t>
+          <t xml:space="preserve">2030-03-13</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,25 +4981,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009443</t>
+          <t xml:space="preserve">9123186</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F100">
-        <v>507</v>
+        <v>7550</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311427845</t>
+          <t xml:space="preserve">311428045</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-13</t>
+          <t xml:space="preserve">2030-03-14</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5031,25 +5031,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013032</t>
+          <t xml:space="preserve">9123186</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F101">
-        <v>634</v>
+        <v>2678</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311427844</t>
+          <t xml:space="preserve">311428043</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-13</t>
+          <t xml:space="preserve">2030-03-14</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016721</t>
+          <t xml:space="preserve">2013725</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5090,16 +5090,16 @@
         </is>
       </c>
       <c r="F102">
-        <v>754</v>
+        <v>471</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311427843</t>
+          <t xml:space="preserve">311428180</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-13</t>
+          <t xml:space="preserve">2030-03-16</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5131,25 +5131,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123186</t>
+          <t xml:space="preserve">9689080</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F103">
-        <v>7550</v>
+        <v>4992</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311428045</t>
+          <t xml:space="preserve">311433225</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-14</t>
+          <t xml:space="preserve">2030-04-17</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123186</t>
+          <t xml:space="preserve">1300247</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F104">
-        <v>2678</v>
+        <v>514</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311428043</t>
+          <t xml:space="preserve">311435811</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-14</t>
+          <t xml:space="preserve">2030-05-04</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,25 +5231,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013725</t>
+          <t xml:space="preserve">2085261</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F105">
-        <v>471</v>
+        <v>382</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311428180</t>
+          <t xml:space="preserve">311435810</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-16</t>
+          <t xml:space="preserve">2030-05-04</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5281,25 +5281,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">9689080</t>
+          <t xml:space="preserve">2084925</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F106">
-        <v>4992</v>
+        <v>586</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311433225</t>
+          <t xml:space="preserve">311437242</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-04-17</t>
+          <t xml:space="preserve">2030-05-12</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5331,25 +5331,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300247</t>
+          <t xml:space="preserve">2084925</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F107">
-        <v>514</v>
+        <v>795</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311435811</t>
+          <t xml:space="preserve">311437240</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-04</t>
+          <t xml:space="preserve">2030-05-12</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5381,25 +5381,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085261</t>
+          <t xml:space="preserve">2087370</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F108">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311435810</t>
+          <t xml:space="preserve">311437248</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-04</t>
+          <t xml:space="preserve">2030-05-12</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5431,20 +5431,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2084925</t>
+          <t xml:space="preserve">2099473</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F109">
-        <v>586</v>
+        <v>1003</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311437242</t>
+          <t xml:space="preserve">311437244</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5481,20 +5481,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2084925</t>
+          <t xml:space="preserve">8042705</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F110">
-        <v>795</v>
+        <v>579</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311437240</t>
+          <t xml:space="preserve">311437243</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5531,25 +5531,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087370</t>
+          <t xml:space="preserve">7295209</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F111">
-        <v>385</v>
+        <v>602</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311437248</t>
+          <t xml:space="preserve">311440303</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-12</t>
+          <t xml:space="preserve">2030-05-28</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2099473</t>
+          <t xml:space="preserve">1302084</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="F112">
-        <v>1003</v>
+        <v>771</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311437244</t>
+          <t xml:space="preserve">311440635</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-12</t>
+          <t xml:space="preserve">2030-05-29</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5631,25 +5631,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8042705</t>
+          <t xml:space="preserve">2089220</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F113">
-        <v>579</v>
+        <v>504</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311437243</t>
+          <t xml:space="preserve">311442579</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-12</t>
+          <t xml:space="preserve">2030-06-10</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5681,25 +5681,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">7295209</t>
+          <t xml:space="preserve">8045419</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F114">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311440303</t>
+          <t xml:space="preserve">311442578</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-28</t>
+          <t xml:space="preserve">2030-06-10</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302084</t>
+          <t xml:space="preserve">1300237</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5740,16 +5740,16 @@
         </is>
       </c>
       <c r="F115">
-        <v>771</v>
+        <v>937</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311440635</t>
+          <t xml:space="preserve">311443511</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-29</t>
+          <t xml:space="preserve">2030-06-15</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2089220</t>
+          <t xml:space="preserve">2013279</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="F116">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311442579</t>
+          <t xml:space="preserve">311443524</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-10</t>
+          <t xml:space="preserve">2030-06-15</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8045419</t>
+          <t xml:space="preserve">2014951</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5840,16 +5840,16 @@
         </is>
       </c>
       <c r="F117">
-        <v>599</v>
+        <v>549</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311442578</t>
+          <t xml:space="preserve">311443507</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-10</t>
+          <t xml:space="preserve">2030-06-15</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300237</t>
+          <t xml:space="preserve">8007543</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5890,11 +5890,11 @@
         </is>
       </c>
       <c r="F118">
-        <v>937</v>
+        <v>572</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443511</t>
+          <t xml:space="preserve">311443504</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013279</t>
+          <t xml:space="preserve">8777683</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5940,11 +5940,11 @@
         </is>
       </c>
       <c r="F119">
-        <v>488</v>
+        <v>382</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443524</t>
+          <t xml:space="preserve">311443510</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5981,20 +5981,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014951</t>
+          <t xml:space="preserve">8777683</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F120">
-        <v>549</v>
+        <v>416</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443507</t>
+          <t xml:space="preserve">311443509</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">8007543</t>
+          <t xml:space="preserve">8777661</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="F121">
-        <v>572</v>
+        <v>1110</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443504</t>
+          <t xml:space="preserve">311447153</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-15</t>
+          <t xml:space="preserve">2030-07-01</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777683</t>
+          <t xml:space="preserve">10228151</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6090,16 +6090,16 @@
         </is>
       </c>
       <c r="F122">
-        <v>382</v>
+        <v>749</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443510</t>
+          <t xml:space="preserve">311451637</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-15</t>
+          <t xml:space="preserve">2030-07-29</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6131,25 +6131,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777683</t>
+          <t xml:space="preserve">2098527</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F123">
-        <v>416</v>
+        <v>627</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443509</t>
+          <t xml:space="preserve">311492842</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-15</t>
+          <t xml:space="preserve">2031-02-04</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777661</t>
+          <t xml:space="preserve">2018039</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6190,16 +6190,16 @@
         </is>
       </c>
       <c r="F124">
-        <v>1110</v>
+        <v>263</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311447153</t>
+          <t xml:space="preserve">311493115</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-01</t>
+          <t xml:space="preserve">2031-02-05</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">10228151</t>
+          <t xml:space="preserve">2086057</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6240,16 +6240,16 @@
         </is>
       </c>
       <c r="F125">
-        <v>749</v>
+        <v>6769</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311451637</t>
+          <t xml:space="preserve">311494342</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-29</t>
+          <t xml:space="preserve">2031-02-10</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6281,25 +6281,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098527</t>
+          <t xml:space="preserve">10228151</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F126">
-        <v>627</v>
+        <v>326</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311492842</t>
+          <t xml:space="preserve">311494603</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-04</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6331,25 +6331,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018039</t>
+          <t xml:space="preserve">8777493</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F127">
-        <v>263</v>
+        <v>810</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311493115</t>
+          <t xml:space="preserve">311494601</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-05</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6381,25 +6381,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086057</t>
+          <t xml:space="preserve">2098527</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F128">
-        <v>6769</v>
+        <v>547</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494342</t>
+          <t xml:space="preserve">311499350</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-10</t>
+          <t xml:space="preserve">2031-03-01</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6431,25 +6431,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">10228151</t>
+          <t xml:space="preserve">2009889</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F129">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494603</t>
+          <t xml:space="preserve">311505510</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6481,25 +6481,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777493</t>
+          <t xml:space="preserve">2016076</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F130">
-        <v>810</v>
+        <v>574</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494601</t>
+          <t xml:space="preserve">311505525</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6531,25 +6531,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098527</t>
+          <t xml:space="preserve">2011846</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F131">
-        <v>547</v>
+        <v>9180</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311499350</t>
+          <t xml:space="preserve">311508956</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-01</t>
+          <t xml:space="preserve">2031-03-31</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6581,25 +6581,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009889</t>
+          <t xml:space="preserve">2011846</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F132">
-        <v>336</v>
+        <v>502</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505511</t>
+          <t xml:space="preserve">311508957</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-22</t>
+          <t xml:space="preserve">2031-03-31</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6631,25 +6631,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016076</t>
+          <t xml:space="preserve">2011846</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F133">
-        <v>574</v>
+        <v>1366</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505526</t>
+          <t xml:space="preserve">311508957</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-22</t>
+          <t xml:space="preserve">2031-03-31</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011846</t>
+          <t xml:space="preserve">2087930</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6690,16 +6690,16 @@
         </is>
       </c>
       <c r="F134">
-        <v>9180</v>
+        <v>667</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508956</t>
+          <t xml:space="preserve">311510221</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-31</t>
+          <t xml:space="preserve">2031-04-06</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6731,25 +6731,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011846</t>
+          <t xml:space="preserve">7101580</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F135">
-        <v>502</v>
+        <v>594</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508958</t>
+          <t xml:space="preserve">311510225</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-31</t>
+          <t xml:space="preserve">2031-04-06</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6781,25 +6781,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011846</t>
+          <t xml:space="preserve">7101580</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F136">
-        <v>1366</v>
+        <v>293</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508959</t>
+          <t xml:space="preserve">311510225</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-31</t>
+          <t xml:space="preserve">2031-04-06</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,20 +6831,20 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087930</t>
+          <t xml:space="preserve">7101580</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F137">
-        <v>667</v>
+        <v>1862</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510221</t>
+          <t xml:space="preserve">311510225</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6881,25 +6881,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">7101580</t>
+          <t xml:space="preserve">9937922</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F138">
-        <v>594</v>
+        <v>336</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510225</t>
+          <t xml:space="preserve">311513436</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-06</t>
+          <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6931,25 +6931,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">7101580</t>
+          <t xml:space="preserve">2017700</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F139">
-        <v>293</v>
+        <v>628</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510225</t>
+          <t xml:space="preserve">311513898</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-06</t>
+          <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6981,25 +6981,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">7101580</t>
+          <t xml:space="preserve">8777610</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F140">
-        <v>1862</v>
+        <v>706</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510225</t>
+          <t xml:space="preserve">311515445</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-06</t>
+          <t xml:space="preserve">2031-04-26</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7031,25 +7031,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">711983, 2088539</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F141">
-        <v>1646</v>
+        <v>1272</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513471</t>
+          <t xml:space="preserve">311523012</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-19</t>
+          <t xml:space="preserve">2031-05-27</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7081,25 +7081,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017700</t>
+          <t xml:space="preserve">711977, 2085091</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F142">
-        <v>628</v>
+        <v>4665</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513898</t>
+          <t xml:space="preserve">311525498</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-20</t>
+          <t xml:space="preserve">2031-06-04</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7131,25 +7131,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777610</t>
+          <t xml:space="preserve">711916, 2085366</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F143">
-        <v>706</v>
+        <v>2041</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311515445</t>
+          <t xml:space="preserve">311526998</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-26</t>
+          <t xml:space="preserve">2031-06-10</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">209314</t>
+          <t xml:space="preserve">9689138, 100531698</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F144">
-        <v>406</v>
+        <v>1212</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516729</t>
+          <t xml:space="preserve">311535541</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-29</t>
+          <t xml:space="preserve">2031-07-13</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7231,25 +7231,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">209704</t>
+          <t xml:space="preserve">712004, 7151669</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F145">
-        <v>1143</v>
+        <v>4854</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311516729</t>
+          <t xml:space="preserve">311582969</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-29</t>
+          <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7281,25 +7281,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">9689138, 100531698</t>
+          <t xml:space="preserve">712004, 7151669</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F146">
-        <v>1212</v>
+        <v>3075</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535541</t>
+          <t xml:space="preserve">311582969</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-13</t>
+          <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7336,11 +7336,11 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F147">
-        <v>4854</v>
+        <v>3586</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -7386,11 +7386,11 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F148">
-        <v>3075</v>
+        <v>4854</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -7431,20 +7431,20 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">712004, 7151669</t>
+          <t xml:space="preserve">712005, 7151760</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F149">
-        <v>3586</v>
+        <v>4854</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582969</t>
+          <t xml:space="preserve">311582964</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">712004, 7151669</t>
+          <t xml:space="preserve">712005, 7151760</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F150">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582969</t>
+          <t xml:space="preserve">311582964</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7536,11 +7536,11 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F151">
-        <v>4854</v>
+        <v>6472</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -7586,11 +7586,11 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F152">
-        <v>4854</v>
+        <v>18836</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -7631,12 +7631,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">712005, 7151760</t>
+          <t xml:space="preserve">712006, 7151761</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F153">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582964</t>
+          <t xml:space="preserve">311582963</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7681,20 +7681,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">712005, 7151760</t>
+          <t xml:space="preserve">712006, 7151761</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F154">
-        <v>18836</v>
+        <v>4854</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582964</t>
+          <t xml:space="preserve">311582963</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7736,11 +7736,11 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F155">
-        <v>6472</v>
+        <v>18836</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -7786,11 +7786,11 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F156">
-        <v>4854</v>
+        <v>4848</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -7831,25 +7831,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">712006, 7151761</t>
+          <t xml:space="preserve">8777493</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F157">
-        <v>18836</v>
+        <v>1330</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582963</t>
+          <t xml:space="preserve">311592665</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-07</t>
+          <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7881,25 +7881,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">712006, 7151761</t>
+          <t xml:space="preserve">712004, 7151669</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F158">
-        <v>4848</v>
+        <v>18833</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582963</t>
+          <t xml:space="preserve">311594594</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-07</t>
+          <t xml:space="preserve">2032-04-22</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7931,25 +7931,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777493</t>
+          <t xml:space="preserve">2016076</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F159">
-        <v>1330</v>
+        <v>1175</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592665</t>
+          <t xml:space="preserve">311600348</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-12</t>
+          <t xml:space="preserve">2032-05-16</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">712004, 7151669</t>
+          <t xml:space="preserve">712003, 7151668</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7990,16 +7990,16 @@
         </is>
       </c>
       <c r="F160">
-        <v>18833</v>
+        <v>18836</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594594</t>
+          <t xml:space="preserve">311651315</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-22</t>
+          <t xml:space="preserve">2032-12-22</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8031,25 +8031,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016076</t>
+          <t xml:space="preserve">712003, 7151668</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F161">
-        <v>1175</v>
+        <v>10498</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311600348</t>
+          <t xml:space="preserve">311651315</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-16</t>
+          <t xml:space="preserve">2032-12-22</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">2087313</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F162">
-        <v>1006</v>
+        <v>517</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646450</t>
+          <t xml:space="preserve">311700222</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-01</t>
+          <t xml:space="preserve">2033-08-15</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8131,25 +8131,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">711912, 2099459</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F163">
-        <v>900</v>
+        <v>1377</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646459</t>
+          <t xml:space="preserve">311710115</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-01</t>
+          <t xml:space="preserve">2033-09-25</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8181,25 +8181,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">711912, 2099459</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F164">
-        <v>900</v>
+        <v>711</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646460</t>
+          <t xml:space="preserve">311710118</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-01</t>
+          <t xml:space="preserve">2033-09-25</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,25 +8231,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">9522598</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F165">
-        <v>1003</v>
+        <v>1385</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647803</t>
+          <t xml:space="preserve">311718754</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-08</t>
+          <t xml:space="preserve">2033-10-31</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,25 +8281,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">2009885</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F166">
-        <v>1003</v>
+        <v>276</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647802</t>
+          <t xml:space="preserve">311720106</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-08</t>
+          <t xml:space="preserve">2033-11-06</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,25 +8331,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">8528063</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F167">
-        <v>900</v>
+        <v>427</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647790</t>
+          <t xml:space="preserve">311723524</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-08</t>
+          <t xml:space="preserve">2033-11-20</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,25 +8381,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">712003, 7151668</t>
+          <t xml:space="preserve">2012391</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F168">
-        <v>18836</v>
+        <v>625</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651315</t>
+          <t xml:space="preserve">311726743</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-22</t>
+          <t xml:space="preserve">2033-12-04</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,25 +8431,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">712003, 7151668</t>
+          <t xml:space="preserve">2012391</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F169">
-        <v>10498</v>
+        <v>638</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651315</t>
+          <t xml:space="preserve">311726742</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-22</t>
+          <t xml:space="preserve">2033-12-04</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8481,25 +8481,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">7003397</t>
+          <t xml:space="preserve">8777389</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F170">
-        <v>6392</v>
+        <v>1582</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311688172</t>
+          <t xml:space="preserve">311727318</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-15</t>
+          <t xml:space="preserve">2033-12-06</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087313</t>
+          <t xml:space="preserve">100061953</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -8540,16 +8540,16 @@
         </is>
       </c>
       <c r="F171">
-        <v>517</v>
+        <v>1456</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311700222</t>
+          <t xml:space="preserve">311728273</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-15</t>
+          <t xml:space="preserve">2033-12-11</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8581,25 +8581,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">711912, 2099459</t>
+          <t xml:space="preserve">7003397</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F172">
-        <v>1377</v>
+        <v>6392</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710115</t>
+          <t xml:space="preserve">311728264</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-25</t>
+          <t xml:space="preserve">2033-12-11</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,25 +8631,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">711912, 2099459</t>
+          <t xml:space="preserve">8777389</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F173">
-        <v>711</v>
+        <v>596</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710118</t>
+          <t xml:space="preserve">311728359</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-25</t>
+          <t xml:space="preserve">2033-12-11</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">8528063</t>
+          <t xml:space="preserve">8777389</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -8690,16 +8690,16 @@
         </is>
       </c>
       <c r="F174">
-        <v>427</v>
+        <v>9380</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718752</t>
+          <t xml:space="preserve">311728358</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-31</t>
+          <t xml:space="preserve">2033-12-11</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8731,25 +8731,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">9522598</t>
+          <t xml:space="preserve">8777389</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F175">
-        <v>1385</v>
+        <v>830</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718754</t>
+          <t xml:space="preserve">311728269</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-31</t>
+          <t xml:space="preserve">2033-12-11</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8781,25 +8781,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009885</t>
+          <t xml:space="preserve">2013620</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F176">
-        <v>276</v>
+        <v>3508</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311720106</t>
+          <t xml:space="preserve">311728546</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-06</t>
+          <t xml:space="preserve">2033-12-12</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8831,25 +8831,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012391</t>
+          <t xml:space="preserve">2087038</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F177">
-        <v>625</v>
+        <v>1219</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726743</t>
+          <t xml:space="preserve">311728681</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-04</t>
+          <t xml:space="preserve">2033-12-13</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8881,25 +8881,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012391</t>
+          <t xml:space="preserve">711991, 7427504</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F178">
-        <v>638</v>
+        <v>548</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726742</t>
+          <t xml:space="preserve">311728678</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-04</t>
+          <t xml:space="preserve">2033-12-13</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8931,25 +8931,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">2016096</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F179">
-        <v>387</v>
+        <v>1032</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726616</t>
+          <t xml:space="preserve">311729104</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-04</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8981,25 +8981,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">711944, 8777637</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F180">
-        <v>2082</v>
+        <v>270</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726596</t>
+          <t xml:space="preserve">311729067</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-04</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9031,25 +9031,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777389</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F181">
-        <v>1582</v>
+        <v>746</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727318</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-06</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">100061953</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F182">
-        <v>1456</v>
+        <v>306</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728273</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-11</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9131,25 +9131,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777389</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F183">
-        <v>596</v>
+        <v>1680</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728359</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-11</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9181,25 +9181,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777389</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F184">
-        <v>9380</v>
+        <v>1646</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728358</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-11</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9231,25 +9231,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777389</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F185">
-        <v>830</v>
+        <v>387</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728269</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-11</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9281,25 +9281,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013620</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F186">
-        <v>3508</v>
+        <v>894</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728546</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-12</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9336,20 +9336,20 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="F187">
-        <v>356</v>
+        <v>1077</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728443</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-12</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9381,25 +9381,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087038</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F188">
-        <v>1219</v>
+        <v>1866</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728681</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-13</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9431,25 +9431,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">711991, 7427504</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="F189">
-        <v>548</v>
+        <v>356</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728678</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-13</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9486,20 +9486,20 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F190">
-        <v>746</v>
+        <v>2082</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728826</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-13</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -9536,20 +9536,20 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F191">
-        <v>894</v>
+        <v>1006</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728910</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-13</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9586,20 +9586,20 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F192">
-        <v>405</v>
+        <v>900</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728825</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-13</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9631,20 +9631,20 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016096</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F193">
-        <v>1032</v>
+        <v>900</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729104</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -9681,20 +9681,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">711944, 8777637</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="F194">
-        <v>270</v>
+        <v>1003</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729067</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -9736,15 +9736,15 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="F195">
-        <v>306</v>
+        <v>1003</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729024</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -9786,15 +9786,15 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="F196">
-        <v>1077</v>
+        <v>900</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729050</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9836,15 +9836,15 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F197">
-        <v>262</v>
+        <v>405</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728983</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -9881,25 +9881,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">7151445</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F198">
-        <v>725</v>
+        <v>262</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729435</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-15</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9931,20 +9931,20 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777493</t>
+          <t xml:space="preserve">7151445</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F199">
-        <v>393</v>
+        <v>725</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729436</t>
+          <t xml:space="preserve">311729435</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -9986,15 +9986,15 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F200">
-        <v>872</v>
+        <v>393</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729438</t>
+          <t xml:space="preserve">311729436</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -10031,25 +10031,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777389</t>
+          <t xml:space="preserve">8777493</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F201">
-        <v>3651</v>
+        <v>872</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730037</t>
+          <t xml:space="preserve">311729438</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-19</t>
+          <t xml:space="preserve">2033-12-15</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -10081,20 +10081,20 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777610</t>
+          <t xml:space="preserve">8777389</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F202">
-        <v>252</v>
+        <v>3651</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730072</t>
+          <t xml:space="preserve">311730037</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123179</t>
+          <t xml:space="preserve">8777610</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -10140,16 +10140,16 @@
         </is>
       </c>
       <c r="F203">
-        <v>5525</v>
+        <v>252</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730993</t>
+          <t xml:space="preserve">311730072</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-22</t>
+          <t xml:space="preserve">2033-12-19</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -10181,25 +10181,25 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123186</t>
+          <t xml:space="preserve">9123179</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F204">
-        <v>1413</v>
+        <v>5525</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311784035</t>
+          <t xml:space="preserve">311730993</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-11</t>
+          <t xml:space="preserve">2033-12-22</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -10231,25 +10231,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013423</t>
+          <t xml:space="preserve">9123186</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F205">
-        <v>10737</v>
+        <v>1413</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311791476</t>
+          <t xml:space="preserve">311784035</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-15</t>
+          <t xml:space="preserve">2034-09-11</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -10286,15 +10286,15 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F206">
-        <v>1176</v>
+        <v>10737</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311791501</t>
+          <t xml:space="preserve">311791476</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -10331,25 +10331,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">7003397</t>
+          <t xml:space="preserve">2013423</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F207">
-        <v>7066</v>
+        <v>1176</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311793436</t>
+          <t xml:space="preserve">311791501</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-25</t>
+          <t xml:space="preserve">2034-10-15</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -10386,15 +10386,15 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F208">
-        <v>9307</v>
+        <v>7066</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311793432</t>
+          <t xml:space="preserve">311793436</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -10431,25 +10431,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300233</t>
+          <t xml:space="preserve">7003397</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F209">
-        <v>4993</v>
+        <v>9307</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800878</t>
+          <t xml:space="preserve">311793432</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-04</t>
+          <t xml:space="preserve">2034-10-25</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -10481,25 +10481,25 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300233</t>
+          <t xml:space="preserve">2099385</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F210">
-        <v>671</v>
+        <v>1460</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800878</t>
+          <t xml:space="preserve">311798580</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-04</t>
+          <t xml:space="preserve">2034-11-21</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -10531,25 +10531,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300233</t>
+          <t xml:space="preserve">2099385</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F211">
-        <v>1431</v>
+        <v>1460</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800878</t>
+          <t xml:space="preserve">311798580</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-04</t>
+          <t xml:space="preserve">2034-11-21</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013620</t>
+          <t xml:space="preserve">1300233</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -10590,11 +10590,11 @@
         </is>
       </c>
       <c r="F212">
-        <v>4085</v>
+        <v>4993</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800877</t>
+          <t xml:space="preserve">311800878</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -10631,20 +10631,20 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013620</t>
+          <t xml:space="preserve">1300233</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F213">
-        <v>2565</v>
+        <v>671</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800876</t>
+          <t xml:space="preserve">311800878</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -10681,20 +10681,20 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016096</t>
+          <t xml:space="preserve">1300233</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F214">
-        <v>7561</v>
+        <v>1431</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800880</t>
+          <t xml:space="preserve">311800878</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -10731,20 +10731,20 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">7003397</t>
+          <t xml:space="preserve">2013620</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F215">
-        <v>1062</v>
+        <v>4085</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800875</t>
+          <t xml:space="preserve">311800877</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -10781,20 +10781,20 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777475</t>
+          <t xml:space="preserve">2013620</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F216">
-        <v>2718</v>
+        <v>2565</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800882</t>
+          <t xml:space="preserve">311800876</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -10831,20 +10831,20 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777475</t>
+          <t xml:space="preserve">2016096</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F217">
-        <v>3350</v>
+        <v>7561</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800882</t>
+          <t xml:space="preserve">311800880</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -10881,20 +10881,20 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777475</t>
+          <t xml:space="preserve">7003397</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F218">
-        <v>361</v>
+        <v>1062</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800884</t>
+          <t xml:space="preserve">311800875</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -10931,25 +10931,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087038</t>
+          <t xml:space="preserve">8777475</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F219">
-        <v>11186</v>
+        <v>2718</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823120</t>
+          <t xml:space="preserve">311800882</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-07</t>
+          <t xml:space="preserve">2034-12-04</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -10981,25 +10981,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">214564</t>
+          <t xml:space="preserve">8777475</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F220">
-        <v>1369</v>
+        <v>3350</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823507</t>
+          <t xml:space="preserve">311800882</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-08</t>
+          <t xml:space="preserve">2034-12-04</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -11031,25 +11031,25 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">214566</t>
+          <t xml:space="preserve">8777475</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F221">
-        <v>2076</v>
+        <v>361</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823503</t>
+          <t xml:space="preserve">311800884</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-08</t>
+          <t xml:space="preserve">2034-12-04</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777417</t>
+          <t xml:space="preserve">2087038</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -11090,16 +11090,16 @@
         </is>
       </c>
       <c r="F222">
-        <v>459</v>
+        <v>11186</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823544</t>
+          <t xml:space="preserve">311823120</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-08</t>
+          <t xml:space="preserve">2035-04-07</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -11131,25 +11131,25 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">214564, 214565</t>
+          <t xml:space="preserve">8777417</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F223">
-        <v>5862</v>
+        <v>459</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824053</t>
+          <t xml:space="preserve">311823544</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-09</t>
+          <t xml:space="preserve">2035-04-08</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -11181,25 +11181,25 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">214588</t>
+          <t xml:space="preserve">2087348</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F224">
-        <v>8344</v>
+        <v>408</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311830603</t>
+          <t xml:space="preserve">311851193</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-09</t>
+          <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -11236,11 +11236,11 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F225">
-        <v>408</v>
+        <v>648</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -11286,11 +11286,11 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F226">
-        <v>648</v>
+        <v>568</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -11336,15 +11336,15 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F227">
-        <v>568</v>
+        <v>728</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851193</t>
+          <t xml:space="preserve">311851197</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -11386,11 +11386,11 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="F228">
-        <v>728</v>
+        <v>648</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -11436,11 +11436,11 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F229">
-        <v>648</v>
+        <v>488</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -11486,11 +11486,11 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F230">
-        <v>488</v>
+        <v>328</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -11536,15 +11536,15 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F231">
-        <v>328</v>
+        <v>2834</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851197</t>
+          <t xml:space="preserve">311851188</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -11586,15 +11586,15 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F232">
-        <v>2834</v>
+        <v>1686</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851188</t>
+          <t xml:space="preserve">311851190</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -11631,20 +11631,20 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087348</t>
+          <t xml:space="preserve">2098044</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F233">
-        <v>1686</v>
+        <v>1944</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851190</t>
+          <t xml:space="preserve">311851178</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -11686,15 +11686,15 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F234">
-        <v>1944</v>
+        <v>2374</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851178</t>
+          <t xml:space="preserve">311851179</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -11736,15 +11736,15 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F235">
-        <v>2374</v>
+        <v>3478</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851179</t>
+          <t xml:space="preserve">311851180</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -11786,15 +11786,15 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F236">
-        <v>3478</v>
+        <v>4327</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851180</t>
+          <t xml:space="preserve">311851182</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -11836,15 +11836,15 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F237">
-        <v>4327</v>
+        <v>750</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851182</t>
+          <t xml:space="preserve">311851184</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -11881,25 +11881,25 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098044</t>
+          <t xml:space="preserve">2099385</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F238">
-        <v>750</v>
+        <v>430</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851184</t>
+          <t xml:space="preserve">311852991</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-25</t>
+          <t xml:space="preserve">2035-09-02</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -11931,25 +11931,25 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2099385</t>
+          <t xml:space="preserve">2098143</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F239">
-        <v>430</v>
+        <v>1146</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852991</t>
+          <t xml:space="preserve">311909814</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-02</t>
+          <t xml:space="preserve">2036-06-22</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">

--- a/public/exports/62761113.xlsx
+++ b/public/exports/62761113.xlsx
@@ -91,17 +91,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobaksvejen 6</t>
+          <t xml:space="preserve">Bagsværd Hovedgade 274</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100321492</t>
+          <t xml:space="preserve">2088080</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -110,7 +110,7 @@
         </is>
       </c>
       <c r="H2">
-        <v>1436</v>
+        <v>360</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fremtidsvej 3</t>
+          <t xml:space="preserve">Batterivej 54</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,16 +161,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100538673</t>
+          <t xml:space="preserve">2014789</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H3">
-        <v>1169</v>
+        <v>1761</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,26 +211,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Værebrovej 82C</t>
+          <t xml:space="preserve">Christianehøj 162</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100891027</t>
+          <t xml:space="preserve">2013432</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H4">
-        <v>387</v>
+        <v>990</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christianehøj 162</t>
+          <t xml:space="preserve">Dynamovej 2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,16 +281,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013432</t>
+          <t xml:space="preserve">711911, 2099464</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H5">
-        <v>990</v>
+        <v>325</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Batterivej 54</t>
+          <t xml:space="preserve">Fremtidsvej 3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014789</t>
+          <t xml:space="preserve">100538673</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H6">
-        <v>1761</v>
+        <v>1169</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllemarken 27A</t>
+          <t xml:space="preserve">Generatorvej 12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017118</t>
+          <t xml:space="preserve">711992, 1302116</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H7">
-        <v>707</v>
+        <v>2013</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,26 +451,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Hovedgade 274</t>
+          <t xml:space="preserve">Gyngemosevej 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088080</t>
+          <t xml:space="preserve">7151446</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="H8">
-        <v>360</v>
+        <v>1085</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,26 +511,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Hovedgade 116</t>
+          <t xml:space="preserve">Høje Gladsaxe 130</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">209314</t>
+          <t xml:space="preserve">8777390</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H9">
-        <v>406</v>
+        <v>691</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,26 +571,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Hovedgade 116</t>
+          <t xml:space="preserve">Høje Gladsaxe Torv 2B</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">209704</t>
+          <t xml:space="preserve">500360, 500361, 500362, 500364, 7151452</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H10">
-        <v>1143</v>
+        <v>5035</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mørkhøj Parkalle 7</t>
+          <t xml:space="preserve">Kagsåkollegiet 106</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,16 +641,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098046</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H11">
-        <v>12973</v>
+        <v>448</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mørkhøj Parkalle 3</t>
+          <t xml:space="preserve">Kagsåkollegiet 111</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098046</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="H12">
-        <v>6908</v>
+        <v>380</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mørkhøj Parkalle 1</t>
+          <t xml:space="preserve">Kagsåkollegiet 122</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,16 +761,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098046</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H13">
-        <v>2492</v>
+        <v>672</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mørkhøj Parkalle 7</t>
+          <t xml:space="preserve">Kagsåkollegiet 146</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,16 +821,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098046</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H14">
-        <v>632</v>
+        <v>448</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turbinevej 10</t>
+          <t xml:space="preserve">Kagsåkollegiet 151</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -881,16 +881,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2099386</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="H15">
-        <v>348</v>
+        <v>400</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frødings Alle 3</t>
+          <t xml:space="preserve">Kagsåkollegiet 153</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,16 +941,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">212352, 212353, 212354, 212355, 212357, 212358, 212356, 212359</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="H16">
-        <v>360</v>
+        <v>306</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,26 +991,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxvej 18</t>
+          <t xml:space="preserve">Kagsåkollegiet 155</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">214564</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H17">
-        <v>1369</v>
+        <v>450</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,26 +1051,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxvej 18</t>
+          <t xml:space="preserve">Kagsåkollegiet 157</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">214564, 214565</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="H18">
-        <v>5862</v>
+        <v>306</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,26 +1111,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxvej 20</t>
+          <t xml:space="preserve">Kagsåkollegiet 159</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">214566</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="H19">
-        <v>2076</v>
+        <v>306</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telefonvej 14</t>
+          <t xml:space="preserve">Kagsåkollegiet 162</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1181,16 +1181,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">214588</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H20">
-        <v>8344</v>
+        <v>672</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søborg Hovedgade 198</t>
+          <t xml:space="preserve">Kagsåkollegiet 18</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">220694, 220695</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H21">
-        <v>1924</v>
+        <v>672</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåvej 97</t>
+          <t xml:space="preserve">Kagsåkollegiet 186</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,16 +1301,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">222533, 222534</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H22">
-        <v>316</v>
+        <v>448</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåvej 93</t>
+          <t xml:space="preserve">Kagsåkollegiet 2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,16 +1361,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">222534</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H23">
-        <v>316</v>
+        <v>448</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe Torv 2B</t>
+          <t xml:space="preserve">Kagsåkollegiet 3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1421,16 +1421,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">500360, 500361, 500362, 500364, 7151452</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H24">
-        <v>5035</v>
+        <v>266</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dynamovej 2</t>
+          <t xml:space="preserve">Kagsåkollegiet 31</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,16 +1481,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">711911, 2099464</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H25">
-        <v>325</v>
+        <v>380</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 106</t>
+          <t xml:space="preserve">Kagsåkollegiet 42</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1546,11 +1546,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H26">
-        <v>448</v>
+        <v>672</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 3</t>
+          <t xml:space="preserve">Kagsåkollegiet 71</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H27">
-        <v>266</v>
+        <v>380</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 31</t>
+          <t xml:space="preserve">Klausdalsbrovej 269</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,16 +1661,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">711942, 9522597</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H28">
-        <v>380</v>
+        <v>312</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,26 +1711,26 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 71</t>
+          <t xml:space="preserve">Møllemarken 27A</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">2017118</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H29">
-        <v>380</v>
+        <v>707</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 111</t>
+          <t xml:space="preserve">Mørkhøj Parkalle 1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1781,16 +1781,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">2098046</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H30">
-        <v>380</v>
+        <v>2492</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 151</t>
+          <t xml:space="preserve">Mørkhøj Parkalle 3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,16 +1841,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">2098046</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H31">
-        <v>400</v>
+        <v>6908</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 153</t>
+          <t xml:space="preserve">Mørkhøj Parkalle 7</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,16 +1901,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">2098046</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H32">
-        <v>306</v>
+        <v>12973</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 155</t>
+          <t xml:space="preserve">Mørkhøj Parkalle 7</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1961,16 +1961,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">2098046</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H33">
-        <v>450</v>
+        <v>632</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 157</t>
+          <t xml:space="preserve">Skolesvinget 4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,16 +2021,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">7151447</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="H34">
-        <v>306</v>
+        <v>1085</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 159</t>
+          <t xml:space="preserve">Tobaksvejen 6</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2081,16 +2081,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">100321492</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H35">
-        <v>306</v>
+        <v>1436</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 42</t>
+          <t xml:space="preserve">Transformervej 15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2141,16 +2141,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">711981, 2099445</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H36">
-        <v>672</v>
+        <v>1020</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 18</t>
+          <t xml:space="preserve">Turbinevej 10</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2201,16 +2201,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">2099386</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H37">
-        <v>672</v>
+        <v>348</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2251,26 +2251,26 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 2</t>
+          <t xml:space="preserve">Valdemar Poulsens Vej 6</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">711990, 2087329</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H38">
-        <v>448</v>
+        <v>2537</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2311,26 +2311,26 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 186</t>
+          <t xml:space="preserve">Værebrovej 82C</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">100891027</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H39">
-        <v>448</v>
+        <v>387</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2371,40 +2371,40 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 162</t>
+          <t xml:space="preserve">Møllemarken 27</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">2017118</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H40">
-        <v>672</v>
+        <v>1200</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200021869</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-10-06</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2431,40 +2431,40 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 146</t>
+          <t xml:space="preserve">Taxvej 25</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">2085364</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H41">
-        <v>448</v>
+        <v>2047</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200024430</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-11-24</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 122</t>
+          <t xml:space="preserve">Buddingevej 222</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,30 +2501,30 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">8705979</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H42">
-        <v>672</v>
+        <v>254</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200024688</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-11-27</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klausdalsbrovej 269</t>
+          <t xml:space="preserve">Ilbjerg Alle 23</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2561,30 +2561,30 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">711942, 9522597</t>
+          <t xml:space="preserve">8777687</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>312</v>
+        <v>10924</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200043875</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-01-04</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformervej 15</t>
+          <t xml:space="preserve">Gyngemose Parkvej 28A</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,30 +2621,30 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">711981, 2099445</t>
+          <t xml:space="preserve">2098038</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H44">
-        <v>1020</v>
+        <v>3669</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200054667</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-11-09</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2671,40 +2671,40 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdemar Poulsens Vej 6</t>
+          <t xml:space="preserve">Kagsåkollegiet 66</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">711990, 2087329</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H45">
-        <v>2537</v>
+        <v>672</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200056559</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-01-10</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generatorvej 12</t>
+          <t xml:space="preserve">Kagsåkollegiet 90</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2741,30 +2741,30 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">711992, 1302116</t>
+          <t xml:space="preserve">711938, 8777432</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H46">
-        <v>2013</v>
+        <v>448</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200056555</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-01-10</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyngemosevej 1</t>
+          <t xml:space="preserve">Høje Gladsaxe Torv 4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2801,30 +2801,30 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">7151446</t>
+          <t xml:space="preserve">8777389</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H47">
-        <v>1085</v>
+        <v>3306</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200057719</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-02-27</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -2851,40 +2851,40 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolesvinget 4</t>
+          <t xml:space="preserve">Værebrovej 156</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">7151447</t>
+          <t xml:space="preserve">2088846</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H48">
-        <v>1085</v>
+        <v>1409</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200057710</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-02-27</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -2911,40 +2911,40 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 130</t>
+          <t xml:space="preserve">Værebrovej 156</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777390</t>
+          <t xml:space="preserve">2088846</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H49">
-        <v>691</v>
+        <v>10147</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200057710</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-02-27</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllemarken 27</t>
+          <t xml:space="preserve">Værebrovej 156</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2981,25 +2981,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017118</t>
+          <t xml:space="preserve">2088846</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H50">
-        <v>1200</v>
+        <v>1955</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021869</t>
+          <t xml:space="preserve">200057708</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-06</t>
+          <t xml:space="preserve">2022-02-27</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxvej 25</t>
+          <t xml:space="preserve">Værebrovej 158A</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3041,25 +3041,25 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085364</t>
+          <t xml:space="preserve">2088846</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H51">
-        <v>2047</v>
+        <v>730</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024430</t>
+          <t xml:space="preserve">200057709</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-24</t>
+          <t xml:space="preserve">2022-02-27</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buddingevej 222</t>
+          <t xml:space="preserve">Wergelands Alle 2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3101,25 +3101,25 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">8705979</t>
+          <t xml:space="preserve">2009784</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H52">
-        <v>254</v>
+        <v>9046</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024688</t>
+          <t xml:space="preserve">200057707</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-27</t>
+          <t xml:space="preserve">2022-02-27</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilbjerg Alle 23</t>
+          <t xml:space="preserve">Frødings Alle 3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777687</t>
+          <t xml:space="preserve">212352, 212353, 212354, 212355, 212357, 212358, 212356, 212359</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3170,16 +3170,16 @@
         </is>
       </c>
       <c r="H53">
-        <v>10924</v>
+        <v>360</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043874</t>
+          <t xml:space="preserve">311084106</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-04</t>
+          <t xml:space="preserve">2024-11-19</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyngemose Parkvej 28A</t>
+          <t xml:space="preserve">Nordvad 9</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3221,35 +3221,35 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098038</t>
+          <t xml:space="preserve">2012604</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H54">
-        <v>3669</v>
+        <v>7984</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054667</t>
+          <t xml:space="preserve">311230939</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-11-09</t>
+          <t xml:space="preserve">2027-02-27</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3271,17 +3271,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 90</t>
+          <t xml:space="preserve">Bagsværd Møllevej 3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">2089300</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3290,26 +3290,26 @@
         </is>
       </c>
       <c r="H55">
-        <v>448</v>
+        <v>1625</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056555</t>
+          <t xml:space="preserve">311242205</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-01-10</t>
+          <t xml:space="preserve">2027-04-21</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kagsåkollegiet 66</t>
+          <t xml:space="preserve">Dynamovej 6</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3341,35 +3341,35 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">711938, 8777432</t>
+          <t xml:space="preserve">711982, 2099475</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H56">
-        <v>672</v>
+        <v>551</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056559</t>
+          <t xml:space="preserve">311356777</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-01-10</t>
+          <t xml:space="preserve">2029-01-28</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wergelands Alle 2</t>
+          <t xml:space="preserve">Pilegårdsvej 100</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009784</t>
+          <t xml:space="preserve">2098100</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3410,26 +3410,26 @@
         </is>
       </c>
       <c r="H57">
-        <v>9046</v>
+        <v>667</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057707</t>
+          <t xml:space="preserve">311365532</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-27</t>
+          <t xml:space="preserve">2029-03-19</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3446,50 +3446,50 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">159</t>
+          <t xml:space="preserve">151</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Værebrovej 156</t>
+          <t xml:space="preserve">Damsagervej 9</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088846</t>
+          <t xml:space="preserve">2109413, 100724820</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H58">
-        <v>1409</v>
+        <v>1554</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057710</t>
+          <t xml:space="preserve">311403334</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-27</t>
+          <t xml:space="preserve">2029-10-11</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Værebrovej 156</t>
+          <t xml:space="preserve">Bagsværd Hovedgade 50</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3521,35 +3521,35 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088846</t>
+          <t xml:space="preserve">7101570</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H59">
-        <v>10147</v>
+        <v>1114</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057710</t>
+          <t xml:space="preserve">311408325</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-27</t>
+          <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3571,45 +3571,45 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Værebrovej 156</t>
+          <t xml:space="preserve">Kildebakken 30</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088846</t>
+          <t xml:space="preserve">2013088</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H60">
-        <v>1955</v>
+        <v>812</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057708</t>
+          <t xml:space="preserve">311408323</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-27</t>
+          <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3631,45 +3631,45 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Værebrovej 158A</t>
+          <t xml:space="preserve">Kildebakken 40</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088846</t>
+          <t xml:space="preserve">2013102</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H61">
-        <v>730</v>
+        <v>275</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057709</t>
+          <t xml:space="preserve">311408322</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-27</t>
+          <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe Torv 4</t>
+          <t xml:space="preserve">Kildebakken 44</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777389</t>
+          <t xml:space="preserve">2013089</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3710,26 +3710,26 @@
         </is>
       </c>
       <c r="H62">
-        <v>3306</v>
+        <v>273</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057719</t>
+          <t xml:space="preserve">311408321</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-27</t>
+          <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3751,17 +3751,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordvad 9</t>
+          <t xml:space="preserve">Vadstrupvej 20A</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012604</t>
+          <t xml:space="preserve">2085304</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3770,16 +3770,16 @@
         </is>
       </c>
       <c r="H63">
-        <v>7984</v>
+        <v>272</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230939</t>
+          <t xml:space="preserve">311408324</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-27</t>
+          <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Møllevej 3</t>
+          <t xml:space="preserve">Bagsværd Hovedgade 86</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2089300</t>
+          <t xml:space="preserve">2086993</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3830,16 +3830,16 @@
         </is>
       </c>
       <c r="H64">
-        <v>1625</v>
+        <v>1194</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242205</t>
+          <t xml:space="preserve">311415734</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-21</t>
+          <t xml:space="preserve">2030-01-03</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3871,35 +3871,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dynamovej 6</t>
+          <t xml:space="preserve">Bagsværd Hovedgade 86</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">711982, 2099475</t>
+          <t xml:space="preserve">2086993</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H65">
-        <v>551</v>
+        <v>499</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311356775</t>
+          <t xml:space="preserve">311415734</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-28</t>
+          <t xml:space="preserve">2030-01-03</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3931,35 +3931,35 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pilegårdsvej 100</t>
+          <t xml:space="preserve">Værebrovej 158</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098100</t>
+          <t xml:space="preserve">2088846</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H66">
-        <v>667</v>
+        <v>2225</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365532</t>
+          <t xml:space="preserve">311415889</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-19</t>
+          <t xml:space="preserve">2030-01-06</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3986,40 +3986,40 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">151</t>
+          <t xml:space="preserve">159</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Damsagervej 9</t>
+          <t xml:space="preserve">Bagsværddal 15</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2109413, 100724820</t>
+          <t xml:space="preserve">2084680</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H67">
-        <v>1554</v>
+        <v>760</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311403334</t>
+          <t xml:space="preserve">311417120</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-11</t>
+          <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakken 30</t>
+          <t xml:space="preserve">Carl Blochs Alle 7</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013088</t>
+          <t xml:space="preserve">2014070</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4070,16 +4070,16 @@
         </is>
       </c>
       <c r="H68">
-        <v>812</v>
+        <v>782</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408323</t>
+          <t xml:space="preserve">311417092</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-11</t>
+          <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakken 44</t>
+          <t xml:space="preserve">Carl Møllers Alle 1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013089</t>
+          <t xml:space="preserve">2014490</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="H69">
-        <v>273</v>
+        <v>2207</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408321</t>
+          <t xml:space="preserve">311417115</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-11</t>
+          <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,35 +4171,35 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakken 40</t>
+          <t xml:space="preserve">Elledalen 8</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013102</t>
+          <t xml:space="preserve">2018039</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H70">
-        <v>275</v>
+        <v>460</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408322</t>
+          <t xml:space="preserve">311417148</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-11</t>
+          <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vadstrupvej 20A</t>
+          <t xml:space="preserve">Gladsaxe Møllevej 65</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085304</t>
+          <t xml:space="preserve">2017046</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4250,16 +4250,16 @@
         </is>
       </c>
       <c r="H71">
-        <v>272</v>
+        <v>329</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408324</t>
+          <t xml:space="preserve">311417095</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-11</t>
+          <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Hovedgade 50</t>
+          <t xml:space="preserve">Kagsåvej 93</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">7101570</t>
+          <t xml:space="preserve">222534</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4310,16 +4310,16 @@
         </is>
       </c>
       <c r="H72">
-        <v>1114</v>
+        <v>316</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408325</t>
+          <t xml:space="preserve">311417100</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-11</t>
+          <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,35 +4351,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Hovedgade 86</t>
+          <t xml:space="preserve">Kagsåvej 97</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086993</t>
+          <t xml:space="preserve">222533, 222534</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H73">
-        <v>1194</v>
+        <v>316</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311415734</t>
+          <t xml:space="preserve">311417100</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-03</t>
+          <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4411,35 +4411,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Hovedgade 86</t>
+          <t xml:space="preserve">Kildebakkegårds Alle 171</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086993</t>
+          <t xml:space="preserve">2013620</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H74">
-        <v>499</v>
+        <v>1400</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311415734</t>
+          <t xml:space="preserve">311417096</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-03</t>
+          <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,35 +4471,35 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Værebrovej 158</t>
+          <t xml:space="preserve">Mørkhøjvej 154</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088846</t>
+          <t xml:space="preserve">7295209</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H75">
-        <v>2225</v>
+        <v>720</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311415889</t>
+          <t xml:space="preserve">311417091</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-06</t>
+          <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakkegårds Alle 171</t>
+          <t xml:space="preserve">Signalvej 95</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4541,20 +4541,20 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013620</t>
+          <t xml:space="preserve">9883414</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H76">
-        <v>1400</v>
+        <v>4672</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417096</t>
+          <t xml:space="preserve">311417114</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Blochs Alle 7</t>
+          <t xml:space="preserve">Søborg Hovedgade 198</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014070</t>
+          <t xml:space="preserve">220694, 220695</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4610,11 +4610,11 @@
         </is>
       </c>
       <c r="H77">
-        <v>782</v>
+        <v>1924</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417092</t>
+          <t xml:space="preserve">311417101</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Møllers Alle 1</t>
+          <t xml:space="preserve">Taxvej 27</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014490</t>
+          <t xml:space="preserve">2085363</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4670,11 +4670,11 @@
         </is>
       </c>
       <c r="H78">
-        <v>2207</v>
+        <v>1927</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417115</t>
+          <t xml:space="preserve">311417112</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxe Møllevej 65</t>
+          <t xml:space="preserve">Kong Hans Alle 43</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4721,25 +4721,25 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017046</t>
+          <t xml:space="preserve">2012391</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H79">
-        <v>329</v>
+        <v>471</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417095</t>
+          <t xml:space="preserve">311418137</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-14</t>
+          <t xml:space="preserve">2030-01-21</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4771,35 +4771,35 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elledalen 8</t>
+          <t xml:space="preserve">Buddinge Hovedgade 111</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018039</t>
+          <t xml:space="preserve">2012253</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H80">
-        <v>460</v>
+        <v>484</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417148</t>
+          <t xml:space="preserve">311418880</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-14</t>
+          <t xml:space="preserve">2030-01-24</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4831,17 +4831,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværddal 15</t>
+          <t xml:space="preserve">Højmarksvej 24</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2084680</t>
+          <t xml:space="preserve">2010230</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="H81">
-        <v>760</v>
+        <v>639</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417120</t>
+          <t xml:space="preserve">311423941</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-14</t>
+          <t xml:space="preserve">2030-02-21</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxvej 27</t>
+          <t xml:space="preserve">Tobaksvejen 24</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085363</t>
+          <t xml:space="preserve">2018588</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="H82">
-        <v>1927</v>
+        <v>895</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417112</t>
+          <t xml:space="preserve">311423940</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-14</t>
+          <t xml:space="preserve">2030-02-21</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mørkhøjvej 154</t>
+          <t xml:space="preserve">Carl Møllers Alle 7</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">7295209</t>
+          <t xml:space="preserve">2011266</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4970,16 +4970,16 @@
         </is>
       </c>
       <c r="H83">
-        <v>720</v>
+        <v>482</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417091</t>
+          <t xml:space="preserve">311424125</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-14</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Signalvej 95</t>
+          <t xml:space="preserve">Christianehøj 164</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">9883414</t>
+          <t xml:space="preserve">2013432</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="H84">
-        <v>4672</v>
+        <v>507</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417114</t>
+          <t xml:space="preserve">311424132</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-14</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Hans Alle 43</t>
+          <t xml:space="preserve">Lauggårds Alle 15</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5081,25 +5081,25 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012391</t>
+          <t xml:space="preserve">2010032</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H85">
-        <v>471</v>
+        <v>731</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418137</t>
+          <t xml:space="preserve">311424128</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-21</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buddinge Hovedgade 111</t>
+          <t xml:space="preserve">Gladsaxevej 200</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012253</t>
+          <t xml:space="preserve">9123186</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5150,16 +5150,16 @@
         </is>
       </c>
       <c r="H86">
-        <v>484</v>
+        <v>6329</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418880</t>
+          <t xml:space="preserve">311425249</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-24</t>
+          <t xml:space="preserve">2030-02-28</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højmarksvej 24</t>
+          <t xml:space="preserve">Gladsaxevej 200C</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5201,25 +5201,25 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010230</t>
+          <t xml:space="preserve">9123186</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H87">
-        <v>639</v>
+        <v>764</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311423941</t>
+          <t xml:space="preserve">311425249</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-21</t>
+          <t xml:space="preserve">2030-02-28</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tobaksvejen 24</t>
+          <t xml:space="preserve">Gladsaxevej 204</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5261,25 +5261,25 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018588</t>
+          <t xml:space="preserve">9123186</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H88">
-        <v>895</v>
+        <v>614</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311423940</t>
+          <t xml:space="preserve">311425251</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-21</t>
+          <t xml:space="preserve">2030-02-28</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lauggårds Alle 15</t>
+          <t xml:space="preserve">Isbanevej 3</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5321,25 +5321,25 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010032</t>
+          <t xml:space="preserve">9123186</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H89">
-        <v>731</v>
+        <v>4930</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424128</t>
+          <t xml:space="preserve">311425249</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2030-02-28</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Møllers Alle 7</t>
+          <t xml:space="preserve">Vandtårnsvej 57</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5381,25 +5381,25 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011266</t>
+          <t xml:space="preserve">9123186</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H90">
-        <v>482</v>
+        <v>2404</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424125</t>
+          <t xml:space="preserve">311425252</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2030-02-28</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christianehøj 164</t>
+          <t xml:space="preserve">Alsikemarken 13</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013432</t>
+          <t xml:space="preserve">2016721</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5450,16 +5450,16 @@
         </is>
       </c>
       <c r="H91">
-        <v>507</v>
+        <v>754</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424132</t>
+          <t xml:space="preserve">311427843</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2030-03-13</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxevej 200</t>
+          <t xml:space="preserve">Solnavej 74B</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123186</t>
+          <t xml:space="preserve">2013032</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5510,16 +5510,16 @@
         </is>
       </c>
       <c r="H92">
-        <v>6329</v>
+        <v>634</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311425249</t>
+          <t xml:space="preserve">311427844</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-28</t>
+          <t xml:space="preserve">2030-03-13</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 57</t>
+          <t xml:space="preserve">Søborghus Alle 23</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5561,25 +5561,25 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123186</t>
+          <t xml:space="preserve">2009443</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H93">
-        <v>2404</v>
+        <v>507</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311425252</t>
+          <t xml:space="preserve">311427845</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-28</t>
+          <t xml:space="preserve">2030-03-13</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxevej 204</t>
+          <t xml:space="preserve">Vandtårnsvej 55</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5626,20 +5626,20 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H94">
-        <v>614</v>
+        <v>7550</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311425251</t>
+          <t xml:space="preserve">311428045</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-28</t>
+          <t xml:space="preserve">2030-03-14</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isbanevej 3</t>
+          <t xml:space="preserve">Vandtårnsvej 55</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5686,20 +5686,20 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H95">
-        <v>4930</v>
+        <v>2678</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311425249</t>
+          <t xml:space="preserve">311428043</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-28</t>
+          <t xml:space="preserve">2030-03-14</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxevej 200C</t>
+          <t xml:space="preserve">Dickens Alle 7</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5741,25 +5741,25 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123186</t>
+          <t xml:space="preserve">2013725</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H96">
-        <v>764</v>
+        <v>471</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311425249</t>
+          <t xml:space="preserve">311428180</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-28</t>
+          <t xml:space="preserve">2030-03-16</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søborghus Alle 23</t>
+          <t xml:space="preserve">Vandtårnsvej 59</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009443</t>
+          <t xml:space="preserve">9689080</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5810,16 +5810,16 @@
         </is>
       </c>
       <c r="H97">
-        <v>507</v>
+        <v>4992</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311427845</t>
+          <t xml:space="preserve">311433225</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-13</t>
+          <t xml:space="preserve">2030-04-17</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,35 +5851,35 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solnavej 74B</t>
+          <t xml:space="preserve">Taxvej 17</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013032</t>
+          <t xml:space="preserve">2085261</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H98">
-        <v>634</v>
+        <v>382</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311427844</t>
+          <t xml:space="preserve">311435810</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-13</t>
+          <t xml:space="preserve">2030-05-04</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alsikemarken 13</t>
+          <t xml:space="preserve">Vadgårdsvej 9</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016721</t>
+          <t xml:space="preserve">1300247</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5930,16 +5930,16 @@
         </is>
       </c>
       <c r="H99">
-        <v>754</v>
+        <v>514</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311427843</t>
+          <t xml:space="preserve">311435811</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-13</t>
+          <t xml:space="preserve">2030-05-04</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5971,35 +5971,35 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 55</t>
+          <t xml:space="preserve">Amundsensvej 13</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123186</t>
+          <t xml:space="preserve">2087370</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H100">
-        <v>7550</v>
+        <v>385</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311428045</t>
+          <t xml:space="preserve">311437248</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-14</t>
+          <t xml:space="preserve">2030-05-12</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 55</t>
+          <t xml:space="preserve">Dickens Alle 13</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6041,25 +6041,25 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123186</t>
+          <t xml:space="preserve">8042705</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H101">
-        <v>2678</v>
+        <v>579</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311428043</t>
+          <t xml:space="preserve">311437243</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-14</t>
+          <t xml:space="preserve">2030-05-12</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6091,35 +6091,35 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dickens Alle 7</t>
+          <t xml:space="preserve">Krakasvej 1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013725</t>
+          <t xml:space="preserve">2084925</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H102">
-        <v>471</v>
+        <v>795</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311428180</t>
+          <t xml:space="preserve">311437240</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-16</t>
+          <t xml:space="preserve">2030-05-12</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,35 +6151,35 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 59</t>
+          <t xml:space="preserve">Krakasvej 3</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9689080</t>
+          <t xml:space="preserve">2084925</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H103">
-        <v>4992</v>
+        <v>586</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311433225</t>
+          <t xml:space="preserve">311437242</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-04-17</t>
+          <t xml:space="preserve">2030-05-12</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vadgårdsvej 9</t>
+          <t xml:space="preserve">Oktobervej 20</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300247</t>
+          <t xml:space="preserve">2099473</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6230,16 +6230,16 @@
         </is>
       </c>
       <c r="H104">
-        <v>514</v>
+        <v>1003</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311435811</t>
+          <t xml:space="preserve">311437244</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-04</t>
+          <t xml:space="preserve">2030-05-12</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6271,17 +6271,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxvej 17</t>
+          <t xml:space="preserve">Mørkhøjvej 330</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085261</t>
+          <t xml:space="preserve">7295209</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6290,16 +6290,16 @@
         </is>
       </c>
       <c r="H105">
-        <v>382</v>
+        <v>602</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311435810</t>
+          <t xml:space="preserve">311440303</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-04</t>
+          <t xml:space="preserve">2030-05-28</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6331,35 +6331,35 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krakasvej 3</t>
+          <t xml:space="preserve">Pilegårdsvej 1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2084925</t>
+          <t xml:space="preserve">1302084</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H106">
-        <v>586</v>
+        <v>771</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311437242</t>
+          <t xml:space="preserve">311440635</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-12</t>
+          <t xml:space="preserve">2030-05-29</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6391,35 +6391,35 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krakasvej 1</t>
+          <t xml:space="preserve">Skovdiget 8</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2084925</t>
+          <t xml:space="preserve">2089220</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H107">
-        <v>795</v>
+        <v>504</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311437240</t>
+          <t xml:space="preserve">311442579</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-12</t>
+          <t xml:space="preserve">2030-06-10</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6451,17 +6451,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amundsensvej 13</t>
+          <t xml:space="preserve">Taxvej 19</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087370</t>
+          <t xml:space="preserve">8045419</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6470,16 +6470,16 @@
         </is>
       </c>
       <c r="H108">
-        <v>385</v>
+        <v>599</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311437248</t>
+          <t xml:space="preserve">311442578</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-12</t>
+          <t xml:space="preserve">2030-06-10</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oktobervej 20</t>
+          <t xml:space="preserve">Esberns Alle 15</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2099473</t>
+          <t xml:space="preserve">1300237</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6530,16 +6530,16 @@
         </is>
       </c>
       <c r="H109">
-        <v>1003</v>
+        <v>937</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311437244</t>
+          <t xml:space="preserve">311443511</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-12</t>
+          <t xml:space="preserve">2030-06-15</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dickens Alle 13</t>
+          <t xml:space="preserve">Gyngemose Parkvej 30</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6581,25 +6581,25 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8042705</t>
+          <t xml:space="preserve">8777683</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H110">
-        <v>579</v>
+        <v>382</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311437243</t>
+          <t xml:space="preserve">311443510</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-12</t>
+          <t xml:space="preserve">2030-06-15</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mørkhøjvej 330</t>
+          <t xml:space="preserve">Gyngemose Parkvej 32</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">7295209</t>
+          <t xml:space="preserve">8777683</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6650,16 +6650,16 @@
         </is>
       </c>
       <c r="H111">
-        <v>602</v>
+        <v>416</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311440303</t>
+          <t xml:space="preserve">311443509</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-28</t>
+          <t xml:space="preserve">2030-06-15</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pilegårdsvej 1</t>
+          <t xml:space="preserve">Kildebakkegårds Alle 166</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302084</t>
+          <t xml:space="preserve">2013279</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6710,16 +6710,16 @@
         </is>
       </c>
       <c r="H112">
-        <v>771</v>
+        <v>488</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311440635</t>
+          <t xml:space="preserve">311443524</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-29</t>
+          <t xml:space="preserve">2030-06-15</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6751,17 +6751,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovdiget 8</t>
+          <t xml:space="preserve">Provst Bentzons Vej 7</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2089220</t>
+          <t xml:space="preserve">2014951</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6770,16 +6770,16 @@
         </is>
       </c>
       <c r="H113">
-        <v>504</v>
+        <v>549</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311442579</t>
+          <t xml:space="preserve">311443507</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-10</t>
+          <t xml:space="preserve">2030-06-15</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taxvej 19</t>
+          <t xml:space="preserve">Slotsparken 31</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">8045419</t>
+          <t xml:space="preserve">8007543</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6830,16 +6830,16 @@
         </is>
       </c>
       <c r="H114">
-        <v>599</v>
+        <v>572</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311442578</t>
+          <t xml:space="preserve">311443504</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-10</t>
+          <t xml:space="preserve">2030-06-15</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6871,17 +6871,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Esberns Alle 15</t>
+          <t xml:space="preserve">Ibsvej 3</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300237</t>
+          <t xml:space="preserve">8777661</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6890,16 +6890,16 @@
         </is>
       </c>
       <c r="H115">
-        <v>937</v>
+        <v>1110</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443511</t>
+          <t xml:space="preserve">311447153</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-15</t>
+          <t xml:space="preserve">2030-07-01</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakkegårds Alle 166</t>
+          <t xml:space="preserve">Gladsaxevej 9</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013279</t>
+          <t xml:space="preserve">10228151</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6950,16 +6950,16 @@
         </is>
       </c>
       <c r="H116">
-        <v>488</v>
+        <v>749</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443524</t>
+          <t xml:space="preserve">311451637</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-15</t>
+          <t xml:space="preserve">2030-07-29</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provst Bentzons Vej 7</t>
+          <t xml:space="preserve">Ilbjerg Alle 38A</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014951</t>
+          <t xml:space="preserve">2098527</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7010,16 +7010,16 @@
         </is>
       </c>
       <c r="H117">
-        <v>549</v>
+        <v>627</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443507</t>
+          <t xml:space="preserve">311492842</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-15</t>
+          <t xml:space="preserve">2031-02-04</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7051,17 +7051,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slotsparken 31</t>
+          <t xml:space="preserve">Elledalen 6</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8007543</t>
+          <t xml:space="preserve">2018039</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7070,16 +7070,16 @@
         </is>
       </c>
       <c r="H118">
-        <v>572</v>
+        <v>263</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443522</t>
+          <t xml:space="preserve">311493115</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-15</t>
+          <t xml:space="preserve">2031-02-05</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7111,17 +7111,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyngemose Parkvej 30</t>
+          <t xml:space="preserve">Triumfvej 1</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777683</t>
+          <t xml:space="preserve">2086057</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7130,16 +7130,16 @@
         </is>
       </c>
       <c r="H119">
-        <v>382</v>
+        <v>6769</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443510</t>
+          <t xml:space="preserve">311494342</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-15</t>
+          <t xml:space="preserve">2031-02-10</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyngemose Parkvej 32</t>
+          <t xml:space="preserve">Gladsaxevej 17</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777683</t>
+          <t xml:space="preserve">10228151</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H120">
-        <v>416</v>
+        <v>326</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443509</t>
+          <t xml:space="preserve">311494603</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-15</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7231,35 +7231,35 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ibsvej 3</t>
+          <t xml:space="preserve">Transformervej 5</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777661</t>
+          <t xml:space="preserve">8777493</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H121">
-        <v>1110</v>
+        <v>810</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311447153</t>
+          <t xml:space="preserve">311494601</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-01</t>
+          <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxevej 9</t>
+          <t xml:space="preserve">Ilbjerg Alle 38B</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7301,25 +7301,25 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">10228151</t>
+          <t xml:space="preserve">2098527</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H122">
-        <v>749</v>
+        <v>547</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311451637</t>
+          <t xml:space="preserve">311499350</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-29</t>
+          <t xml:space="preserve">2031-03-01</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilbjerg Alle 38A</t>
+          <t xml:space="preserve">Frødings Alle 4</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7361,25 +7361,25 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098527</t>
+          <t xml:space="preserve">2009889</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H123">
-        <v>627</v>
+        <v>336</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311492842</t>
+          <t xml:space="preserve">311505511</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-04</t>
+          <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7411,35 +7411,35 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elledalen 6</t>
+          <t xml:space="preserve">Klausdalsbrovej 195</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018039</t>
+          <t xml:space="preserve">2016076</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H124">
-        <v>263</v>
+        <v>574</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311493115</t>
+          <t xml:space="preserve">311505526</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-05</t>
+          <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7471,17 +7471,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triumfvej 1</t>
+          <t xml:space="preserve">Gladsaxevej 198</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086057</t>
+          <t xml:space="preserve">2011846</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7490,16 +7490,16 @@
         </is>
       </c>
       <c r="H125">
-        <v>6769</v>
+        <v>9180</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494342</t>
+          <t xml:space="preserve">311508956</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-10</t>
+          <t xml:space="preserve">2031-03-31</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxevej 17</t>
+          <t xml:space="preserve">Gladsaxevej 198</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7541,25 +7541,25 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">10228151</t>
+          <t xml:space="preserve">2011846</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H126">
-        <v>326</v>
+        <v>502</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494603</t>
+          <t xml:space="preserve">311508958</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2031-03-31</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformervej 5</t>
+          <t xml:space="preserve">Gladsaxevej 198</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7601,25 +7601,25 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777493</t>
+          <t xml:space="preserve">2011846</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H127">
-        <v>810</v>
+        <v>1366</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311494601</t>
+          <t xml:space="preserve">311508959</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-11</t>
+          <t xml:space="preserve">2031-03-31</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7651,35 +7651,35 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilbjerg Alle 38B</t>
+          <t xml:space="preserve">Nybrovej 321</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2098527</t>
+          <t xml:space="preserve">7101580</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H128">
-        <v>547</v>
+        <v>594</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311499350</t>
+          <t xml:space="preserve">311510225</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-01</t>
+          <t xml:space="preserve">2031-04-06</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7711,17 +7711,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frødings Alle 4</t>
+          <t xml:space="preserve">Nybrovej 331</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009889</t>
+          <t xml:space="preserve">7101580</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -7730,16 +7730,16 @@
         </is>
       </c>
       <c r="H129">
-        <v>336</v>
+        <v>293</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505510</t>
+          <t xml:space="preserve">311510225</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-22</t>
+          <t xml:space="preserve">2031-04-06</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -7771,35 +7771,35 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klausdalsbrovej 195</t>
+          <t xml:space="preserve">Nybrovej 333</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016076</t>
+          <t xml:space="preserve">7101580</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H130">
-        <v>574</v>
+        <v>1862</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505526</t>
+          <t xml:space="preserve">311510225</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-22</t>
+          <t xml:space="preserve">2031-04-06</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7831,17 +7831,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxevej 198</t>
+          <t xml:space="preserve">Slotsparken 30</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011846</t>
+          <t xml:space="preserve">2087930</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -7850,16 +7850,16 @@
         </is>
       </c>
       <c r="H131">
-        <v>9180</v>
+        <v>667</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508956</t>
+          <t xml:space="preserve">311510221</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-31</t>
+          <t xml:space="preserve">2031-04-06</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7891,35 +7891,35 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxevej 198</t>
+          <t xml:space="preserve">Bagsværdvej 138A</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011846</t>
+          <t xml:space="preserve">9937922</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H132">
-        <v>502</v>
+        <v>336</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508957</t>
+          <t xml:space="preserve">311513436</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-31</t>
+          <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7951,35 +7951,35 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxevej 198</t>
+          <t xml:space="preserve">Tjele Alle 11</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011846</t>
+          <t xml:space="preserve">2017700</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H133">
-        <v>1366</v>
+        <v>628</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508959</t>
+          <t xml:space="preserve">311513898</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-31</t>
+          <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8011,17 +8011,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slotsparken 30</t>
+          <t xml:space="preserve">Bagsværdvej 144A</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087930</t>
+          <t xml:space="preserve">8777610</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8030,16 +8030,16 @@
         </is>
       </c>
       <c r="H134">
-        <v>667</v>
+        <v>706</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510221</t>
+          <t xml:space="preserve">311515445</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-06</t>
+          <t xml:space="preserve">2031-04-26</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8071,35 +8071,35 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 321</t>
+          <t xml:space="preserve">Bagsværd Hovedgade 116</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7101580</t>
+          <t xml:space="preserve">209314</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H135">
-        <v>594</v>
+        <v>406</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510225</t>
+          <t xml:space="preserve">311516729</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-06</t>
+          <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8131,35 +8131,35 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 331</t>
+          <t xml:space="preserve">Bagsværd Hovedgade 116</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">7101580</t>
+          <t xml:space="preserve">209704</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H136">
-        <v>293</v>
+        <v>1143</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510225</t>
+          <t xml:space="preserve">311516729</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-06</t>
+          <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8191,35 +8191,35 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 333</t>
+          <t xml:space="preserve">Skovalleen 38B</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">7101580</t>
+          <t xml:space="preserve">711983, 2088539</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H137">
-        <v>1862</v>
+        <v>1272</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510225</t>
+          <t xml:space="preserve">311523012</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-06</t>
+          <t xml:space="preserve">2031-05-27</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8251,35 +8251,35 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværdvej 138A</t>
+          <t xml:space="preserve">Skovdiget 1</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">9937922</t>
+          <t xml:space="preserve">711977, 2085091</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H138">
-        <v>336</v>
+        <v>4665</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513436</t>
+          <t xml:space="preserve">311525498</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-19</t>
+          <t xml:space="preserve">2031-06-04</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8311,35 +8311,35 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjele Alle 11</t>
+          <t xml:space="preserve">Granvej 53</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017700</t>
+          <t xml:space="preserve">711916, 2085366</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H139">
-        <v>628</v>
+        <v>2041</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513898</t>
+          <t xml:space="preserve">311526998</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-20</t>
+          <t xml:space="preserve">2031-06-10</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8371,17 +8371,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværdvej 144A</t>
+          <t xml:space="preserve">Vandtårnsvej 61</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777610</t>
+          <t xml:space="preserve">9689138, 100531698</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -8390,16 +8390,16 @@
         </is>
       </c>
       <c r="H140">
-        <v>706</v>
+        <v>1212</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311515445</t>
+          <t xml:space="preserve">311535541</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-26</t>
+          <t xml:space="preserve">2031-07-13</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8431,35 +8431,35 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovalleen 38B</t>
+          <t xml:space="preserve">Høje Gladsaxe 1</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">711983, 2088539</t>
+          <t xml:space="preserve">712006, 7151761</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H141">
-        <v>1272</v>
+        <v>18836</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311523012</t>
+          <t xml:space="preserve">311582963</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-27</t>
+          <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8491,35 +8491,35 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovdiget 1</t>
+          <t xml:space="preserve">Høje Gladsaxe 106</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">711977, 2085091</t>
+          <t xml:space="preserve">712004, 7151669</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="H142">
-        <v>4665</v>
+        <v>3586</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311525498</t>
+          <t xml:space="preserve">311582969</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-04</t>
+          <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8551,17 +8551,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Granvej 53</t>
+          <t xml:space="preserve">Høje Gladsaxe 11</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">711916, 2085366</t>
+          <t xml:space="preserve">712005, 7151760</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -8570,16 +8570,16 @@
         </is>
       </c>
       <c r="H143">
-        <v>2041</v>
+        <v>18836</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526998</t>
+          <t xml:space="preserve">311582964</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-10</t>
+          <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 61</t>
+          <t xml:space="preserve">Høje Gladsaxe 116</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8621,25 +8621,25 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9689138, 100531698</t>
+          <t xml:space="preserve">712004, 7151669</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="H144">
-        <v>1212</v>
+        <v>4854</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535541</t>
+          <t xml:space="preserve">311582969</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-13</t>
+          <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 84</t>
+          <t xml:space="preserve">Høje Gladsaxe 16</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8681,20 +8681,20 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">712004, 7151669</t>
+          <t xml:space="preserve">712006, 7151761</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H145">
-        <v>4854</v>
+        <v>6472</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582969</t>
+          <t xml:space="preserve">311582963</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 96</t>
+          <t xml:space="preserve">Høje Gladsaxe 32</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8741,20 +8741,20 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">712004, 7151669</t>
+          <t xml:space="preserve">712006, 7151761</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H146">
-        <v>3075</v>
+        <v>4854</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582969</t>
+          <t xml:space="preserve">311582963</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 106</t>
+          <t xml:space="preserve">Høje Gladsaxe 4</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8801,20 +8801,20 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">712004, 7151669</t>
+          <t xml:space="preserve">712006, 7151761</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H147">
-        <v>3586</v>
+        <v>4848</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582969</t>
+          <t xml:space="preserve">311582963</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 116</t>
+          <t xml:space="preserve">Høje Gladsaxe 44</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">712004, 7151669</t>
+          <t xml:space="preserve">712005, 7151760</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H148">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582969</t>
+          <t xml:space="preserve">311582964</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 44</t>
+          <t xml:space="preserve">Høje Gladsaxe 56</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H149">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 56</t>
+          <t xml:space="preserve">Høje Gladsaxe 68</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8986,11 +8986,11 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H150">
-        <v>4854</v>
+        <v>6472</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 68</t>
+          <t xml:space="preserve">Høje Gladsaxe 84</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">712005, 7151760</t>
+          <t xml:space="preserve">712004, 7151669</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -9050,11 +9050,11 @@
         </is>
       </c>
       <c r="H151">
-        <v>6472</v>
+        <v>4854</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582964</t>
+          <t xml:space="preserve">311582969</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 11</t>
+          <t xml:space="preserve">Høje Gladsaxe 96</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9101,20 +9101,20 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">712005, 7151760</t>
+          <t xml:space="preserve">712004, 7151669</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H152">
-        <v>18836</v>
+        <v>3075</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582964</t>
+          <t xml:space="preserve">311582969</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 16</t>
+          <t xml:space="preserve">Transformervej 3</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9161,25 +9161,25 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">712006, 7151761</t>
+          <t xml:space="preserve">8777493</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H153">
-        <v>6472</v>
+        <v>1330</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582963</t>
+          <t xml:space="preserve">311592665</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-07</t>
+          <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 32</t>
+          <t xml:space="preserve">Høje Gladsaxe 21</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9221,25 +9221,25 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">712006, 7151761</t>
+          <t xml:space="preserve">712004, 7151669</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H154">
-        <v>4854</v>
+        <v>18833</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582963</t>
+          <t xml:space="preserve">311594594</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-07</t>
+          <t xml:space="preserve">2032-04-22</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 1</t>
+          <t xml:space="preserve">Klausdalsbrovej 197</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9281,25 +9281,25 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">712006, 7151761</t>
+          <t xml:space="preserve">2016076</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H155">
-        <v>18836</v>
+        <v>1175</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582963</t>
+          <t xml:space="preserve">311600348</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-07</t>
+          <t xml:space="preserve">2032-05-16</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 4</t>
+          <t xml:space="preserve">Høje Gladsaxe 31</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9341,25 +9341,25 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">712006, 7151761</t>
+          <t xml:space="preserve">712003, 7151668</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H156">
-        <v>4848</v>
+        <v>18836</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582963</t>
+          <t xml:space="preserve">311651315</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-07</t>
+          <t xml:space="preserve">2032-12-22</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformervej 3</t>
+          <t xml:space="preserve">Høje Gladsaxe 51</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9401,25 +9401,25 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777493</t>
+          <t xml:space="preserve">712003, 7151668</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H157">
-        <v>1330</v>
+        <v>10498</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592665</t>
+          <t xml:space="preserve">311651315</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-12</t>
+          <t xml:space="preserve">2032-12-22</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -9451,35 +9451,35 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 21</t>
+          <t xml:space="preserve">Nybrovej 356</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">712004, 7151669</t>
+          <t xml:space="preserve">2087313</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H158">
-        <v>18833</v>
+        <v>517</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594594</t>
+          <t xml:space="preserve">311700222</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-22</t>
+          <t xml:space="preserve">2033-08-15</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klausdalsbrovej 197</t>
+          <t xml:space="preserve">Dynamovej 5</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9521,25 +9521,25 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016076</t>
+          <t xml:space="preserve">711912, 2099459</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H159">
-        <v>1175</v>
+        <v>1377</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311600348</t>
+          <t xml:space="preserve">311710115</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-16</t>
+          <t xml:space="preserve">2033-09-25</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 31</t>
+          <t xml:space="preserve">Dynamovej 5</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9581,25 +9581,25 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">712003, 7151668</t>
+          <t xml:space="preserve">711912, 2099459</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H160">
-        <v>18836</v>
+        <v>711</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651315</t>
+          <t xml:space="preserve">311710118</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-22</t>
+          <t xml:space="preserve">2033-09-25</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 51</t>
+          <t xml:space="preserve">Klausdalsbrovej 271</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9641,25 +9641,25 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">712003, 7151668</t>
+          <t xml:space="preserve">9522598</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H161">
-        <v>10498</v>
+        <v>1385</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651315</t>
+          <t xml:space="preserve">311718754</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-22</t>
+          <t xml:space="preserve">2033-10-31</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -9691,17 +9691,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 356</t>
+          <t xml:space="preserve">Frødings Alle 8</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087313</t>
+          <t xml:space="preserve">2009885</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -9710,16 +9710,16 @@
         </is>
       </c>
       <c r="H162">
-        <v>517</v>
+        <v>276</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311700222</t>
+          <t xml:space="preserve">311720106</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-15</t>
+          <t xml:space="preserve">2033-11-06</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dynamovej 5</t>
+          <t xml:space="preserve">Kildebakkegårds Alle 125</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9761,25 +9761,25 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">711912, 2099459</t>
+          <t xml:space="preserve">8528063</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H163">
-        <v>1377</v>
+        <v>427</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710115</t>
+          <t xml:space="preserve">311723524</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-25</t>
+          <t xml:space="preserve">2033-11-20</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dynamovej 5</t>
+          <t xml:space="preserve">Kong Hans Alle 45</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9821,25 +9821,25 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">711912, 2099459</t>
+          <t xml:space="preserve">2012391</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H164">
-        <v>711</v>
+        <v>625</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710118</t>
+          <t xml:space="preserve">311726743</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-25</t>
+          <t xml:space="preserve">2033-12-04</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klausdalsbrovej 271</t>
+          <t xml:space="preserve">Kong Hans Alle 47</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9881,25 +9881,25 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">9522598</t>
+          <t xml:space="preserve">2012391</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H165">
-        <v>1385</v>
+        <v>638</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718754</t>
+          <t xml:space="preserve">311726742</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-31</t>
+          <t xml:space="preserve">2033-12-04</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frødings Alle 8</t>
+          <t xml:space="preserve">Skolesvinget 10</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9941,25 +9941,25 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009885</t>
+          <t xml:space="preserve">8777389</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H166">
-        <v>276</v>
+        <v>1582</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311720106</t>
+          <t xml:space="preserve">311727318</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-06</t>
+          <t xml:space="preserve">2033-12-06</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakkegårds Alle 125</t>
+          <t xml:space="preserve">Høje Gladsaxe Torv 4</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10001,25 +10001,25 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">8528063</t>
+          <t xml:space="preserve">8777389</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H167">
-        <v>427</v>
+        <v>596</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723524</t>
+          <t xml:space="preserve">311728359</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-20</t>
+          <t xml:space="preserve">2033-12-11</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Hans Alle 45</t>
+          <t xml:space="preserve">Høje Gladsaxe Torv 4</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10061,25 +10061,25 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012391</t>
+          <t xml:space="preserve">8777389</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H168">
-        <v>625</v>
+        <v>9380</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726743</t>
+          <t xml:space="preserve">311728358</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-04</t>
+          <t xml:space="preserve">2033-12-11</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Hans Alle 47</t>
+          <t xml:space="preserve">Rådhus Alle 5</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10121,25 +10121,25 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012391</t>
+          <t xml:space="preserve">7003397</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H169">
-        <v>638</v>
+        <v>6392</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726742</t>
+          <t xml:space="preserve">311728264</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-04</t>
+          <t xml:space="preserve">2033-12-11</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolesvinget 10</t>
+          <t xml:space="preserve">Skolesvinget 15</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10181,25 +10181,25 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777389</t>
+          <t xml:space="preserve">100061953</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H170">
-        <v>1582</v>
+        <v>1456</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727318</t>
+          <t xml:space="preserve">311728273</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-06</t>
+          <t xml:space="preserve">2033-12-11</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolesvinget 15</t>
+          <t xml:space="preserve">Skolesvinget 9</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10241,20 +10241,20 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">100061953</t>
+          <t xml:space="preserve">8777389</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H171">
-        <v>1456</v>
+        <v>830</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728273</t>
+          <t xml:space="preserve">311728269</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhus Alle 5</t>
+          <t xml:space="preserve">Søborg Hovedgade 190</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10301,25 +10301,25 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">7003397</t>
+          <t xml:space="preserve">2013620</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H172">
-        <v>6392</v>
+        <v>3508</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728264</t>
+          <t xml:space="preserve">311728546</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-11</t>
+          <t xml:space="preserve">2033-12-12</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -10351,35 +10351,35 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe Torv 4</t>
+          <t xml:space="preserve">Bagsværd Hovedgade 60F</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777389</t>
+          <t xml:space="preserve">2087038</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H173">
-        <v>596</v>
+        <v>1219</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728359</t>
+          <t xml:space="preserve">311728681</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-11</t>
+          <t xml:space="preserve">2033-12-13</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -10411,35 +10411,35 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe Torv 4</t>
+          <t xml:space="preserve">Nybrovej 384</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777389</t>
+          <t xml:space="preserve">711991, 7427504</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H174">
-        <v>9380</v>
+        <v>548</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728358</t>
+          <t xml:space="preserve">311728678</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-11</t>
+          <t xml:space="preserve">2033-12-13</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -10471,35 +10471,35 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolesvinget 9</t>
+          <t xml:space="preserve">Gammelmosevej 51A</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777389</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H175">
-        <v>830</v>
+        <v>1646</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728269</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-11</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søborg Hovedgade 190</t>
+          <t xml:space="preserve">Gladsaxe Møllevej 127</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013620</t>
+          <t xml:space="preserve">2016096</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -10550,16 +10550,16 @@
         </is>
       </c>
       <c r="H176">
-        <v>3508</v>
+        <v>1032</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728546</t>
+          <t xml:space="preserve">311729104</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-12</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -10591,35 +10591,35 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Hovedgade 60F</t>
+          <t xml:space="preserve">Kellersvej 1</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087038</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H177">
-        <v>1219</v>
+        <v>387</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728681</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-13</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -10651,35 +10651,35 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 384</t>
+          <t xml:space="preserve">Kellersvej 10</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">711991, 7427504</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H178">
-        <v>548</v>
+        <v>306</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728678</t>
+          <t xml:space="preserve">311729024</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-13</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxe Møllevej 127</t>
+          <t xml:space="preserve">Kellersvej 11</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10721,20 +10721,20 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016096</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="H179">
-        <v>1032</v>
+        <v>900</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729104</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10771,30 +10771,30 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongshvilebakken 8</t>
+          <t xml:space="preserve">Kellersvej 12</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">711944, 8777637</t>
+          <t xml:space="preserve">8777413</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="H180">
-        <v>270</v>
+        <v>356</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729067</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 20A</t>
+          <t xml:space="preserve">Kellersvej 13</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10846,11 +10846,11 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="H181">
-        <v>746</v>
+        <v>900</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 10</t>
+          <t xml:space="preserve">Kellersvej 14</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10906,11 +10906,11 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="H182">
-        <v>306</v>
+        <v>894</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdemars Alle 81</t>
+          <t xml:space="preserve">Kellersvej 15</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10966,11 +10966,11 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="H183">
-        <v>1680</v>
+        <v>1003</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelmosevej 51A</t>
+          <t xml:space="preserve">Kellersvej 16</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -11026,15 +11026,15 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="H184">
-        <v>1646</v>
+        <v>1077</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728977</t>
+          <t xml:space="preserve">311729050</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 1</t>
+          <t xml:space="preserve">Kellersvej 17</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11086,11 +11086,11 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="H185">
-        <v>387</v>
+        <v>1003</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 14</t>
+          <t xml:space="preserve">Kellersvej 18</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11146,15 +11146,15 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H186">
-        <v>894</v>
+        <v>262</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728977</t>
+          <t xml:space="preserve">311728983</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 16</t>
+          <t xml:space="preserve">Kellersvej 19</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11206,11 +11206,11 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="H187">
-        <v>1077</v>
+        <v>900</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 3</t>
+          <t xml:space="preserve">Kellersvej 2</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11266,11 +11266,11 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H188">
-        <v>1866</v>
+        <v>405</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 12</t>
+          <t xml:space="preserve">Kellersvej 20A</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11326,11 +11326,11 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H189">
-        <v>356</v>
+        <v>746</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 6A</t>
+          <t xml:space="preserve">Kellersvej 3</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11386,11 +11386,11 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H190">
-        <v>2082</v>
+        <v>1866</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 9</t>
+          <t xml:space="preserve">Kellersvej 6A</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11446,11 +11446,11 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="H191">
-        <v>1006</v>
+        <v>2082</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 11</t>
+          <t xml:space="preserve">Kellersvej 9</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11506,11 +11506,11 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="H192">
-        <v>900</v>
+        <v>1006</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -11551,30 +11551,30 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 13</t>
+          <t xml:space="preserve">Kongshvilebakken 8</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">711944, 8777637</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H193">
-        <v>900</v>
+        <v>270</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728977</t>
+          <t xml:space="preserve">311729067</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 15</t>
+          <t xml:space="preserve">Valdemars Alle 81</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11626,11 +11626,11 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H194">
-        <v>1003</v>
+        <v>1680</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 17</t>
+          <t xml:space="preserve">Høje Gladsaxe 71</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -11681,25 +11681,25 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">7151445</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H195">
-        <v>1003</v>
+        <v>725</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728977</t>
+          <t xml:space="preserve">311729435</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2033-12-15</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 19</t>
+          <t xml:space="preserve">Transformervej 1</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11741,25 +11741,25 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">8777493</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H196">
-        <v>900</v>
+        <v>393</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728977</t>
+          <t xml:space="preserve">311729436</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2033-12-15</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 2</t>
+          <t xml:space="preserve">Transformervej 1B</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -11801,25 +11801,25 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">8777493</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H197">
-        <v>405</v>
+        <v>872</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728977</t>
+          <t xml:space="preserve">311729438</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2033-12-15</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -11851,35 +11851,35 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kellersvej 18</t>
+          <t xml:space="preserve">Bagsværdvej 144B</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777413</t>
+          <t xml:space="preserve">8777610</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H198">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728977</t>
+          <t xml:space="preserve">311730072</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2033-12-19</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Gladsaxe 71</t>
+          <t xml:space="preserve">Skolesvinget 8</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -11921,25 +11921,25 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">7151445</t>
+          <t xml:space="preserve">8777389</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H199">
-        <v>725</v>
+        <v>3651</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729435</t>
+          <t xml:space="preserve">311730037</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-15</t>
+          <t xml:space="preserve">2033-12-19</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformervej 1</t>
+          <t xml:space="preserve">Isbanevej 8</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -11981,25 +11981,25 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777493</t>
+          <t xml:space="preserve">9123179</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H200">
-        <v>393</v>
+        <v>5525</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729436</t>
+          <t xml:space="preserve">311730993</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-15</t>
+          <t xml:space="preserve">2033-12-22</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transformervej 1B</t>
+          <t xml:space="preserve">Vandtårnsvej 55B</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12041,25 +12041,25 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777493</t>
+          <t xml:space="preserve">9123186</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="H201">
-        <v>872</v>
+        <v>1413</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729438</t>
+          <t xml:space="preserve">311784035</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-15</t>
+          <t xml:space="preserve">2034-09-11</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolesvinget 8</t>
+          <t xml:space="preserve">Kildebakkegårds Alle 155</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -12101,25 +12101,25 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777389</t>
+          <t xml:space="preserve">2013423</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H202">
-        <v>3651</v>
+        <v>10737</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730037</t>
+          <t xml:space="preserve">311791476</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-19</t>
+          <t xml:space="preserve">2034-10-15</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -12151,35 +12151,35 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværdvej 144B</t>
+          <t xml:space="preserve">Kildebakkegårds Alle 155</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2860</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777610</t>
+          <t xml:space="preserve">2013423</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H203">
-        <v>252</v>
+        <v>1176</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730072</t>
+          <t xml:space="preserve">311791501</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-19</t>
+          <t xml:space="preserve">2034-10-15</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isbanevej 8</t>
+          <t xml:space="preserve">Rådhus Alle 7</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -12221,25 +12221,25 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123179</t>
+          <t xml:space="preserve">7003397</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H204">
-        <v>5525</v>
+        <v>7066</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730993</t>
+          <t xml:space="preserve">311793436</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-22</t>
+          <t xml:space="preserve">2034-10-25</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandtårnsvej 55B</t>
+          <t xml:space="preserve">Rådhuspassagen 6</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -12281,25 +12281,25 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">9123186</t>
+          <t xml:space="preserve">7003397</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H205">
-        <v>1413</v>
+        <v>9307</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311784035</t>
+          <t xml:space="preserve">311793432</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-11</t>
+          <t xml:space="preserve">2034-10-25</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakkegårds Alle 155</t>
+          <t xml:space="preserve">Turbinevej 12</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013423</t>
+          <t xml:space="preserve">2099385</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -12350,16 +12350,16 @@
         </is>
       </c>
       <c r="H206">
-        <v>10737</v>
+        <v>1460</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311791476</t>
+          <t xml:space="preserve">311798580</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-15</t>
+          <t xml:space="preserve">2034-11-21</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakkegårds Alle 155</t>
+          <t xml:space="preserve">Turbinevej 12</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -12401,7 +12401,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013423</t>
+          <t xml:space="preserve">2099385</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -12410,16 +12410,16 @@
         </is>
       </c>
       <c r="H207">
-        <v>1176</v>
+        <v>1460</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311791501</t>
+          <t xml:space="preserve">311798580</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-15</t>
+          <t xml:space="preserve">2034-11-21</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhus Alle 7</t>
+          <t xml:space="preserve">Gladsaxe Møllevej 127</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">7003397</t>
+          <t xml:space="preserve">2016096</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -12470,16 +12470,16 @@
         </is>
       </c>
       <c r="H208">
-        <v>7066</v>
+        <v>7561</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311793436</t>
+          <t xml:space="preserve">311800880</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-25</t>
+          <t xml:space="preserve">2034-12-04</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhuspassagen 6</t>
+          <t xml:space="preserve">Kildebakkegårds Alle 165</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -12521,25 +12521,25 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">7003397</t>
+          <t xml:space="preserve">2013620</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H209">
-        <v>9307</v>
+        <v>4085</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311793432</t>
+          <t xml:space="preserve">311800877</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-25</t>
+          <t xml:space="preserve">2034-12-04</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turbinevej 12</t>
+          <t xml:space="preserve">Kildebakkegårds Alle 165</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -12581,25 +12581,25 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2099385</t>
+          <t xml:space="preserve">2013620</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H210">
-        <v>1460</v>
+        <v>2565</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311798580</t>
+          <t xml:space="preserve">311800876</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-21</t>
+          <t xml:space="preserve">2034-12-04</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turbinevej 12</t>
+          <t xml:space="preserve">Klausdalsbrovej 213</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -12641,25 +12641,25 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2099385</t>
+          <t xml:space="preserve">8777475</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H211">
-        <v>1460</v>
+        <v>2718</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311798580</t>
+          <t xml:space="preserve">311800882</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-21</t>
+          <t xml:space="preserve">2034-12-04</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Hans Alle 32</t>
+          <t xml:space="preserve">Klausdalsbrovej 213</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -12701,20 +12701,20 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300233</t>
+          <t xml:space="preserve">8777475</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H212">
-        <v>4993</v>
+        <v>3350</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800878</t>
+          <t xml:space="preserve">311800882</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kong Hans Alle 32</t>
+          <t xml:space="preserve">Klausdalsbrovej 213</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -12761,20 +12761,20 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300233</t>
+          <t xml:space="preserve">8777475</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H213">
-        <v>671</v>
+        <v>361</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800878</t>
+          <t xml:space="preserve">311800884</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -12826,11 +12826,11 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H214">
-        <v>1431</v>
+        <v>4993</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakkegårds Alle 165</t>
+          <t xml:space="preserve">Kong Hans Alle 32</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -12881,20 +12881,20 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013620</t>
+          <t xml:space="preserve">1300233</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H215">
-        <v>4085</v>
+        <v>671</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800877</t>
+          <t xml:space="preserve">311800878</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildebakkegårds Alle 165</t>
+          <t xml:space="preserve">Kong Hans Alle 32</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013620</t>
+          <t xml:space="preserve">1300233</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -12950,11 +12950,11 @@
         </is>
       </c>
       <c r="H216">
-        <v>2565</v>
+        <v>1431</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800876</t>
+          <t xml:space="preserve">311800878</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxe Møllevej 127</t>
+          <t xml:space="preserve">Rådhus Alle 3</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -13001,20 +13001,20 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016096</t>
+          <t xml:space="preserve">7003397</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H217">
-        <v>7561</v>
+        <v>1062</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800880</t>
+          <t xml:space="preserve">311800875</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -13051,35 +13051,35 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhus Alle 3</t>
+          <t xml:space="preserve">Bagsværd Hovedgade 60</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">7003397</t>
+          <t xml:space="preserve">2087038</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H218">
-        <v>1062</v>
+        <v>11186</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800875</t>
+          <t xml:space="preserve">311823120</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-04</t>
+          <t xml:space="preserve">2035-04-07</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -13111,35 +13111,35 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klausdalsbrovej 213</t>
+          <t xml:space="preserve">Taxvej 18</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777475</t>
+          <t xml:space="preserve">214564</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H219">
-        <v>2718</v>
+        <v>1369</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800882</t>
+          <t xml:space="preserve">311823507</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-04</t>
+          <t xml:space="preserve">2035-04-08</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -13171,35 +13171,35 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klausdalsbrovej 213</t>
+          <t xml:space="preserve">Taxvej 20</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2860</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777475</t>
+          <t xml:space="preserve">214566</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H220">
-        <v>3350</v>
+        <v>2076</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800882</t>
+          <t xml:space="preserve">311823503</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-04</t>
+          <t xml:space="preserve">2035-04-08</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klausdalsbrovej 213</t>
+          <t xml:space="preserve">Vadbro 37</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -13241,25 +13241,25 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777475</t>
+          <t xml:space="preserve">8777417</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H221">
-        <v>361</v>
+        <v>459</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800884</t>
+          <t xml:space="preserve">311823544</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-04</t>
+          <t xml:space="preserve">2035-04-08</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Hovedgade 60</t>
+          <t xml:space="preserve">Taxvej 18</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -13301,25 +13301,25 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2087038</t>
+          <t xml:space="preserve">214564, 214565</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H222">
-        <v>11186</v>
+        <v>5862</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823120</t>
+          <t xml:space="preserve">311824053</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-07</t>
+          <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vadbro 37</t>
+          <t xml:space="preserve">Telefonvej 14</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -13361,25 +13361,25 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">8777417</t>
+          <t xml:space="preserve">214588</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H223">
-        <v>459</v>
+        <v>8344</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823544</t>
+          <t xml:space="preserve">311830603</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-08</t>
+          <t xml:space="preserve">2035-05-09</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -13411,7 +13411,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Møllevej 9</t>
+          <t xml:space="preserve">Bagsværd Møllevej 11</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -13426,15 +13426,15 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="H224">
-        <v>408</v>
+        <v>1686</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851193</t>
+          <t xml:space="preserve">311851190</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -13486,11 +13486,11 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="H225">
-        <v>648</v>
+        <v>408</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -13546,11 +13546,11 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="H226">
-        <v>568</v>
+        <v>648</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -13606,15 +13606,15 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="H227">
-        <v>728</v>
+        <v>568</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851197</t>
+          <t xml:space="preserve">311851193</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -13666,11 +13666,11 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="H228">
-        <v>648</v>
+        <v>728</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
@@ -13726,11 +13726,11 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="H229">
-        <v>488</v>
+        <v>648</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
@@ -13786,11 +13786,11 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="H230">
-        <v>328</v>
+        <v>488</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
@@ -13846,15 +13846,15 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="H231">
-        <v>2834</v>
+        <v>328</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851188</t>
+          <t xml:space="preserve">311851197</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagsværd Møllevej 11</t>
+          <t xml:space="preserve">Bagsværd Møllevej 9</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -13906,15 +13906,15 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="H232">
-        <v>1686</v>
+        <v>2834</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851190</t>
+          <t xml:space="preserve">311851188</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">

--- a/public/exports/62761113.xlsx
+++ b/public/exports/62761113.xlsx
@@ -2574,7 +2574,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043875</t>
+          <t xml:space="preserve">200043874</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311356777</t>
+          <t xml:space="preserve">311356775</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443504</t>
+          <t xml:space="preserve">311443522</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505511</t>
+          <t xml:space="preserve">311505510</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508956</t>
+          <t xml:space="preserve">311508960</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508958</t>
+          <t xml:space="preserve">311508960</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729024</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729050</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11154,7 +11154,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728983</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">

--- a/public/exports/62761113.xlsx
+++ b/public/exports/62761113.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L239"/>
+  <dimension ref="A1:M239"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-10-06</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kuben Management A/S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-24</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kuben Management A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-27</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-01-04</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-11-09</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-01-10</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-01-10</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-02-27</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-02-27</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-02-27</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-02-27</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-02-27</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-02-27</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bang &amp; Beenfeldt A/S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-11-19</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-27</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-21</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3354,20 +3629,25 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311356775</t>
+          <t xml:space="preserve">311356777</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-01-28</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-19</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group af 2017 ApS</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-10-11</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-03</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-03</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-06</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-21</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-24</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-21</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-21</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-28</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-28</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-28</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-28</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-02-28</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-13</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-13</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-13</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-14</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-14</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-16</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-04-17</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-04</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-04</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-12</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-12</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-12</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-12</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-12</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-28</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-29</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-06-10</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-06-10</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-06-15</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-06-15</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-06-15</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-06-15</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-06-15</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-06-15</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-07-01</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-07-29</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-04</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-05</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-10</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-11</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-01</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-31</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-31</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7614,20 +8244,25 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508959</t>
+          <t xml:space="preserve">311508960</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-31</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-06</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-06</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-06</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-06</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-19</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">Isolink ApS</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-20</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-26</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-29</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-27</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-04</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-10</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-13</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-07</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådgivende Ingeniør Ole Lentz ApS</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9234,20 +9999,25 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594594</t>
+          <t xml:space="preserve">311594599</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-22</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rådgivende Ingeniør Ole Lentz ApS</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-16</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-22</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-22</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-15</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norca ApS</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-25</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norca ApS</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-25</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-31</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-06</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-20</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-04</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-04</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-06</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-11</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-11</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-11</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-11</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-11</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-12</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-13</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-13</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11034,20 +11949,25 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728977</t>
+          <t xml:space="preserve">311729050</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-15</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-15</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-15</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-19</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-19</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-22</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.F. Byggeservice ApS</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-11</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-15</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-15</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-25</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-25</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-21</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-21</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-04</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-04</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-04</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-04</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-04</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12779,15 +13839,20 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-04</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12839,15 +13904,20 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-04</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-04</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-04</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-04</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13079,15 +14164,20 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-07</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13139,15 +14229,20 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-08</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13199,15 +14294,20 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-08</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13259,15 +14359,20 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-08</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13319,15 +14424,20 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13379,15 +14489,20 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-09</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13439,15 +14554,20 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13499,15 +14619,20 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13559,15 +14684,20 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13619,15 +14749,20 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13679,15 +14814,20 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13739,15 +14879,20 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13799,15 +14944,20 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13859,15 +15009,20 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13919,15 +15074,20 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13979,15 +15139,20 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14039,15 +15204,20 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14099,15 +15269,20 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14159,15 +15334,20 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14219,15 +15399,20 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14279,15 +15464,20 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-02</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14339,21 +15529,26 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norconsult Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-22</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L239" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L239"/>
+  <autoFilter ref="A1:M239"/>
 </worksheet>
 </file>
--- a/public/exports/62761113.xlsx
+++ b/public/exports/62761113.xlsx
@@ -3629,7 +3629,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311356777</t>
+          <t xml:space="preserve">311356775</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311425251</t>
+          <t xml:space="preserve">311425249</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311425252</t>
+          <t xml:space="preserve">311425249</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311443522</t>
+          <t xml:space="preserve">311443504</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505526</t>
+          <t xml:space="preserve">311505525</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508960</t>
+          <t xml:space="preserve">311508956</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508960</t>
+          <t xml:space="preserve">311508957</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311508960</t>
+          <t xml:space="preserve">311508957</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594599</t>
+          <t xml:space="preserve">311594594</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729050</t>
+          <t xml:space="preserve">311728977</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K184" t="inlineStr">
